--- a/out/result.xlsx
+++ b/out/result.xlsx
@@ -7,18 +7,19 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Строки" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Книги" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Дубли" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Спорные" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Задание 2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Как читать" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Строки" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Книги" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Дубли" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Спорные" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Задание 2" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Строки'!$A$1:$S$151</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Книги'!$A$1:$I$92</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Дубли'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спорные'!$A$1:$F$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Задание 2'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Строки'!$A$1:$S$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Книги'!$A$1:$I$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Дубли'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спорные'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Задание 2'!$A$1:$M$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,13 +28,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,9 +69,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -435,6 +441,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="160" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Как читать эту таблицу</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Строки: все строки исходного листа "Задание 1". Слева исходные значения и номер строки, справа очищенные поля, ID книги, дубли, пометки и результат проверки страницы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Книги: каталог после объединения. ID книги считается из очищенных автора и названия, поэтому при добавлении строк не меняется.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Дубли: та же страница (ключ адреса без зеркал s4., www., index.php и слеша в конце) для той же книги. Первая строка основная.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Спорные: строки, где данные или сама страница вызывают вопрос, и каких данных не хватает, чтобы его закрыть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Задание 2: исходный лист с заполненными колонками статуса и признаков, плюс статус страницы, извлечённые данные, совпадение с каталогом и причина.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Нормализация: лишние пробелы и знаки по краям убраны, псевдоним в скобках вынесен отдельно. Названия сравниваются только по буквам и цифрам без пробелов, ё равно е. Автор сравнивается по набору слов без учёта порядка и инициалов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Статусы проверки страницы: 1 найдено совпадение и признаки размещения, 0 совпадение или размещение не подтверждено, 2 автоматически определить не удалось.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:S151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -460,176 +545,176 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Строка в исходнике</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Правообладатель</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Автор</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Тип контента</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Автор (чистый)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Псевдоним</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Название (чистое)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Ключ страницы</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>ID книги</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Дубль строки</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Слов названия в адресе, %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Пометки</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Спорно</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Проверка страницы: статус</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Проверка страницы: причина</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Книга на странице (ID)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Disciplimit</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>dolinakursov.ru</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Disciplimit</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Bdbd1d7</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="n">
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -936,79 +1021,79 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Armine Grigoryan</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Ставка на любовь</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>mp3deer.cc</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Armine Grigoryan</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Ставка на любовь</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>B6b715d</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="n">
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t>Сайт ответил ошибкой 403, содержимое не получено.</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1224,79 +1309,79 @@
       <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Findroid</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>musportal.pro</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Findroid</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>B55d926</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="n">
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание mp3; аудио, слушать онлайн.</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="3" t="inlineStr">
         <is>
           <t>B55d926</t>
         </is>
@@ -1453,79 +1538,79 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Ася Исай</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>https://kniganet.ru/romani/izmena-hochu-tvoego-muzha/</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>kniganet.ru</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Ася Исай</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>kniganet.ru/romani/izmena-hochu-tvoego-muzha</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>B12bf0a</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr"/>
-      <c r="N14" s="2" t="n">
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O14" s="2" t="inlineStr"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="Q14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1678,79 +1763,79 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Helga D.B.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Анталион</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>https://librain.ru/boevik/antalion-mest</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>librain.ru</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>Helga D.B.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr"/>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Анталион</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>librain.ru/boevik/antalion-mest</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>B9411d3</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="n">
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>возможно, тот же автор, что Helga Duran</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="Q17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t>B9411d3</t>
         </is>
@@ -2359,85 +2444,85 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Disciplimit</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>dolinakursov.ru</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Disciplimit</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr"/>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>Bdbd1d7</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n">
+      <c r="M26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="N26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" s="3" t="inlineStr">
         <is>
           <t>дубль строки 2</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="Q26" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R26" s="2" t="inlineStr">
+      <c r="R26" s="3" t="inlineStr">
         <is>
           <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2740,79 +2825,79 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Ira Kiba</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Кармические узлы в натальной карте</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>https://astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>astro-babylon.ru</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Ira Kiba</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Кармические узлы в натальной карте</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Bd0d430</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="n">
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr">
+      <c r="O31" s="3" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="n">
+      <c r="Q31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="R31" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Кармическая астрология | Книги по кармической астрологии</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr"/>
+      <c r="S31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2890,79 +2975,79 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Jana Denole Яна Деноль</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Gaunerinnen</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>https://read.xbook.life/books_gaunerinnen_67131402</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>read.xbook.life</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Jana Denole Яна Деноль</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>Gaunerinnen</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>read.xbook.life/books_gaunerinnen_67131402</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>B754fe1</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="n">
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr">
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>в поле автора два написания, латиницей и кириллицей</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="Q33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: текст книги прямо на странице.</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t>B754fe1</t>
         </is>
@@ -3040,85 +3125,85 @@
       <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Armine Grigoryan</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Ставка на любовь</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>mp3deer.cc</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Armine Grigoryan</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Ставка на любовь</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>B6b715d</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n">
+      <c r="M35" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="N35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="O35" s="3" t="inlineStr">
         <is>
           <t>дубль строки 7</t>
         </is>
       </c>
-      <c r="P35" s="2" t="inlineStr">
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="n">
+      <c r="Q35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="R35" s="3" t="inlineStr">
         <is>
           <t>Сайт ответил ошибкой 403, содержимое не получено.</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr"/>
+      <c r="S35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3646,79 +3731,79 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Lanpirot</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>https://free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2/</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Lanpirot</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>Bd824ca</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="n">
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr">
         <is>
           <t>номер тома или части в адресе другой: в названии 6</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="Q43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="S43" s="3" t="inlineStr">
         <is>
           <t>B6ea970</t>
         </is>
@@ -3946,154 +4031,154 @@
       <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Larisa Lubimova</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>https://librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>librain.ru</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t>Larisa Lubimova</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
         </is>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>B3e0b7a</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="n">
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 39% слов)</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="n">
+      <c r="Q47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="R47" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы. Часть 2: читать и скачать онлайн бесп</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Елена Полярная</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>https://librain.ru/index.php/detektivy/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>librain.ru</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>Елена Полярная</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>librain.ru/detektivy/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="L48" s="2" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>B2f3969</t>
         </is>
       </c>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="n">
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O48" s="2" t="inlineStr"/>
-      <c r="P48" s="2" t="inlineStr">
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
+      <c r="Q48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
+      <c r="S48" s="3" t="inlineStr">
         <is>
           <t>B0930d2</t>
         </is>
@@ -4248,229 +4333,229 @@
       <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Lilit Khachinyan</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Guide de préparation à la production orale du DELF B2</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>https://languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2/</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>languagelearning.site</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>Lilit Khachinyan</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>Guide de préparation à la production orale du DELF B2</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2</t>
         </is>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>B757f18</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="n">
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr">
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 40% слов)</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="n">
+      <c r="Q51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R51" s="2" t="inlineStr">
+      <c r="R51" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Préparation à l’examen du DELF B2 – Language Learning</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr"/>
+      <c r="S51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>Lost In Space</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Наследник, которого не должно быть</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>https://mp3deer.cc/mp3/%D1%81%D1%83%D0%BF%D0%B5%D1%80-%D0%B0%D1%83%D0%B4%D0%B8%D0%BE%D0%BA%D0%BD%D0%B8%D0%B3%D0%B0-%D0%BD%D0%B0%D1%81%D0%BB%D0%B5%D0%B4%D0%BD%D0%B8%D0%BA-%D0%BA%D0%BE%D1%82%D0%BE%D1%80%D0%BE%D0%B3%D0%BE-%D0%BD%D0%B5-%D0%B4%D0%BE%D0%BB%D0%B6%D0%BD%D0%BE-%D0%B1%D1%8B%D1%82%D1%8C</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>mp3deer.cc</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>Lost In Space</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr"/>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>Наследник, которого не должно быть</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
         <is>
           <t>mp3deer.cc/mp3/супер-аудиокнига-наследник-которого-не-должно-быть</t>
         </is>
       </c>
-      <c r="L52" s="2" t="inlineStr">
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>Bea9d0e</t>
         </is>
       </c>
-      <c r="M52" s="2" t="inlineStr"/>
-      <c r="N52" s="2" t="n">
+      <c r="M52" s="3" t="inlineStr"/>
+      <c r="N52" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O52" s="2" t="inlineStr"/>
-      <c r="P52" s="2" t="inlineStr">
+      <c r="O52" s="3" t="inlineStr"/>
+      <c r="P52" s="3" t="inlineStr">
         <is>
           <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="n">
+      <c r="Q52" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R52" s="2" t="inlineStr">
+      <c r="R52" s="3" t="inlineStr">
         <is>
           <t>Сайт ответил ошибкой 403, содержимое не получено.</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr"/>
+      <c r="S52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Lucy Zen</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Автономия</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>https://skladmk.online/product/energiya-zhizni-lucy-zen/</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>skladmk.online</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t>Lucy Zen</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr"/>
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>Автономия</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>skladmk.online/product/energiya-zhizni-lucy-zen</t>
         </is>
       </c>
-      <c r="L53" s="2" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>B419f77</t>
         </is>
       </c>
-      <c r="M53" s="2" t="inlineStr"/>
-      <c r="N53" s="2" t="n">
+      <c r="M53" s="3" t="inlineStr"/>
+      <c r="N53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O53" s="2" t="inlineStr"/>
-      <c r="P53" s="2" t="inlineStr">
+      <c r="O53" s="3" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="n">
+      <c r="Q53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R53" s="2" t="inlineStr">
+      <c r="R53" s="3" t="inlineStr">
         <is>
           <t>Страницы нет: ответ 200, Ошибка | Не удается получить доступ к сайту.</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr"/>
+      <c r="S53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4684,85 +4769,85 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Julia Shi. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>MILA NENKA</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>https://2ivdel.tvoysadik.ru/?section_id=98</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>2ivdel.tvoysadik.ru</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>MILA NENKA</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr"/>
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
         <is>
           <t>2ivdel.tvoysadik.ru?section_id=98</t>
         </is>
       </c>
-      <c r="L57" s="2" t="inlineStr">
+      <c r="L57" s="3" t="inlineStr">
         <is>
           <t>Bf1ba79</t>
         </is>
       </c>
-      <c r="M57" s="2" t="inlineStr"/>
-      <c r="N57" s="2" t="n">
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O57" s="2" t="inlineStr"/>
-      <c r="P57" s="2" t="inlineStr">
+      <c r="O57" s="3" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="n">
+      <c r="Q57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R57" s="2" t="inlineStr">
+      <c r="R57" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Занимательные раскраски</t>
         </is>
       </c>
-      <c r="S57" s="2" t="inlineStr"/>
+      <c r="S57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5203,85 +5288,85 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Findroid</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>musportal.pro</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H64" s="3" t="inlineStr">
         <is>
           <t>Findroid</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
         <is>
           <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
         <is>
           <t>musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
         </is>
       </c>
-      <c r="L64" s="2" t="inlineStr">
+      <c r="L64" s="3" t="inlineStr">
         <is>
           <t>B55d926</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n">
+      <c r="M64" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="N64" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="O64" s="3" t="inlineStr">
         <is>
           <t>дубль строки 11</t>
         </is>
       </c>
-      <c r="P64" s="2" t="inlineStr">
+      <c r="P64" s="3" t="inlineStr">
         <is>
           <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
+      <c r="Q64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание mp3; аудио, слушать онлайн.</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr">
+      <c r="S64" s="3" t="inlineStr">
         <is>
           <t>B55d926</t>
         </is>
@@ -5438,154 +5523,154 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Quartz Y</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Переход в 5D измерение. Просветление. Методичка</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>https://librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>librain.ru</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Quartz Y</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>Переход в 5D измерение. Просветление. Методичка</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr">
         <is>
           <t>librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
         </is>
       </c>
-      <c r="L67" s="2" t="inlineStr">
+      <c r="L67" s="3" t="inlineStr">
         <is>
           <t>B97d1d3</t>
         </is>
       </c>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="n">
+      <c r="M67" s="3" t="inlineStr"/>
+      <c r="N67" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="O67" s="2" t="inlineStr"/>
-      <c r="P67" s="2" t="inlineStr">
+      <c r="O67" s="3" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 25% слов)</t>
         </is>
       </c>
-      <c r="Q67" s="2" t="n">
+      <c r="Q67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R67" s="2" t="inlineStr">
+      <c r="R67" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полност</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr"/>
+      <c r="S67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Rais Ais Gu</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>https://skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854/</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>skladchik.tv</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H68" s="3" t="inlineStr">
         <is>
           <t>Rais Ais Gu</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K68" s="3" t="inlineStr">
         <is>
           <t>skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854</t>
         </is>
       </c>
-      <c r="L68" s="2" t="inlineStr">
+      <c r="L68" s="3" t="inlineStr">
         <is>
           <t>B7ea5ec</t>
         </is>
       </c>
-      <c r="M68" s="2" t="inlineStr"/>
-      <c r="N68" s="2" t="n">
+      <c r="M68" s="3" t="inlineStr"/>
+      <c r="N68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O68" s="2" t="inlineStr"/>
-      <c r="P68" s="2" t="inlineStr">
+      <c r="O68" s="3" t="inlineStr"/>
+      <c r="P68" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="n">
+      <c r="Q68" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R68" s="2" t="inlineStr">
+      <c r="R68" s="3" t="inlineStr">
         <is>
           <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr"/>
+      <c r="S68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6028,164 +6113,164 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Julia Shi. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Констебль. Том III</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>ruslibrary.org</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>Констебль. Том III</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
         <is>
           <t>ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr">
+      <c r="L75" s="3" t="inlineStr">
         <is>
           <t>B10fce6</t>
         </is>
       </c>
-      <c r="M75" s="2" t="inlineStr"/>
-      <c r="N75" s="2" t="n">
+      <c r="M75" s="3" t="inlineStr"/>
+      <c r="N75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O75" s="2" t="inlineStr"/>
-      <c r="P75" s="2" t="inlineStr">
+      <c r="O75" s="3" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R75" s="2" t="inlineStr">
+      <c r="Q75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в тексте страницы (сборник или список), автор совпал. Признаки размещения: скачивание mp3, zip; файлообменники htfl.net, nitroflare.com, trbt.cc; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S75" s="2" t="inlineStr">
+      <c r="S75" s="3" t="inlineStr">
         <is>
           <t>B10fce6</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Ravenna</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Медовичок</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>https://litbox.pro/tag/ravenna/</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>litbox.pro</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H76" s="3" t="inlineStr">
         <is>
           <t>Ravenna</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>Медовичок</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="3" t="inlineStr">
         <is>
           <t>litbox.pro/tag/ravenna</t>
         </is>
       </c>
-      <c r="L76" s="2" t="inlineStr">
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>B02ee1a</t>
         </is>
       </c>
-      <c r="M76" s="2" t="inlineStr"/>
-      <c r="N76" s="2" t="n">
+      <c r="M76" s="3" t="inlineStr"/>
+      <c r="N76" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O76" s="2" t="inlineStr"/>
-      <c r="P76" s="2" t="inlineStr">
+      <c r="O76" s="3" t="inlineStr"/>
+      <c r="P76" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="n">
+      <c r="Q76" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R76" s="2" t="inlineStr">
+      <c r="R76" s="3" t="inlineStr">
         <is>
           <t>Книга есть только в списке на странице автора или подборки, файлов к ней не видно. Нужна проверка человеком.</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr">
+      <c r="S76" s="3" t="inlineStr">
         <is>
           <t>B144a58</t>
         </is>
@@ -6257,85 +6342,85 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Галина Колоскова</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>https://mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>mir-chitki.com</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t>Галина Колоскова</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
         <is>
           <t>mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
         </is>
       </c>
-      <c r="L78" s="2" t="inlineStr">
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>B134592</t>
         </is>
       </c>
-      <c r="M78" s="2" t="inlineStr"/>
-      <c r="N78" s="2" t="n">
+      <c r="M78" s="3" t="inlineStr"/>
+      <c r="N78" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O78" s="2" t="inlineStr"/>
-      <c r="P78" s="2" t="inlineStr">
+      <c r="O78" s="3" t="inlineStr"/>
+      <c r="P78" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
         </is>
       </c>
-      <c r="Q78" s="2" t="n">
+      <c r="Q78" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr"/>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6474,7 +6559,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S80" t="inlineStr"/>
@@ -6551,85 +6636,85 @@
       <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Констебль. Том III</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>ruslibrary.org</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H82" s="3" t="inlineStr">
         <is>
           <t>Vector</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>Констебль. Том III</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="3" t="inlineStr">
         <is>
           <t>ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
         </is>
       </c>
-      <c r="L82" s="2" t="inlineStr">
+      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>B10fce6</t>
         </is>
       </c>
-      <c r="M82" s="2" t="n">
+      <c r="M82" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="N82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O82" s="3" t="inlineStr">
         <is>
           <t>дубль строки 75</t>
         </is>
       </c>
-      <c r="P82" s="2" t="inlineStr">
+      <c r="P82" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" s="2" t="inlineStr">
+      <c r="Q82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R82" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в тексте страницы (сборник или список), автор совпал. Признаки размещения: скачивание mp3, zip; файлообменники htfl.net, nitroflare.com, trbt.cc; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr">
+      <c r="S82" s="3" t="inlineStr">
         <is>
           <t>B10fce6</t>
         </is>
@@ -6938,304 +7023,304 @@
       <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>https://free-kniga.ru/romany/tsena-proscheniya-147884/</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="K87" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru/romany/tsena-proscheniya-147884</t>
         </is>
       </c>
-      <c r="L87" s="2" t="inlineStr">
+      <c r="L87" s="3" t="inlineStr">
         <is>
           <t>Bffdbc8</t>
         </is>
       </c>
-      <c r="M87" s="2" t="inlineStr"/>
-      <c r="N87" s="2" t="n">
+      <c r="M87" s="3" t="inlineStr"/>
+      <c r="N87" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O87" s="2" t="inlineStr"/>
-      <c r="P87" s="2" t="inlineStr">
+      <c r="O87" s="3" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q87" s="2" t="n">
+      <c r="Q87" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R87" s="2" t="inlineStr">
+      <c r="R87" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
         </is>
       </c>
-      <c r="S87" s="2" t="inlineStr"/>
+      <c r="S87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>https://gigabooks.ru/romany/tsena-proscheniya-686299/</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>gigabooks.ru</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K88" s="3" t="inlineStr">
         <is>
           <t>gigabooks.ru/romany/tsena-proscheniya-686299</t>
         </is>
       </c>
-      <c r="L88" s="2" t="inlineStr">
+      <c r="L88" s="3" t="inlineStr">
         <is>
           <t>Bffdbc8</t>
         </is>
       </c>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="n">
+      <c r="M88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O88" s="2" t="inlineStr"/>
-      <c r="P88" s="2" t="inlineStr">
+      <c r="O88" s="3" t="inlineStr"/>
+      <c r="P88" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q88" s="2" t="n">
+      <c r="Q88" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R88" s="2" t="inlineStr">
+      <c r="R88" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
         </is>
       </c>
-      <c r="S88" s="2" t="inlineStr"/>
+      <c r="S88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>https://librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>librain.ru</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K89" s="3" t="inlineStr">
         <is>
           <t>librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
         </is>
       </c>
-      <c r="L89" s="2" t="inlineStr">
+      <c r="L89" s="3" t="inlineStr">
         <is>
           <t>Bffdbc8</t>
         </is>
       </c>
-      <c r="M89" s="2" t="inlineStr"/>
-      <c r="N89" s="2" t="n">
+      <c r="M89" s="3" t="inlineStr"/>
+      <c r="N89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O89" s="2" t="inlineStr"/>
-      <c r="P89" s="2" t="inlineStr">
+      <c r="O89" s="3" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q89" s="2" t="n">
+      <c r="Q89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R89" s="2" t="inlineStr">
+      <c r="R89" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
         </is>
       </c>
-      <c r="S89" s="2" t="inlineStr"/>
+      <c r="S89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>https://litseries.ru/romany/tsena-proscheniya-203253/</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>litseries.ru</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
         <is>
           <t>litseries.ru/romany/tsena-proscheniya-203253</t>
         </is>
       </c>
-      <c r="L90" s="2" t="inlineStr">
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>Bffdbc8</t>
         </is>
       </c>
-      <c r="M90" s="2" t="inlineStr"/>
-      <c r="N90" s="2" t="n">
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O90" s="2" t="inlineStr"/>
-      <c r="P90" s="2" t="inlineStr">
+      <c r="O90" s="3" t="inlineStr"/>
+      <c r="P90" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q90" s="2" t="n">
+      <c r="Q90" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R90" s="2" t="inlineStr">
+      <c r="R90" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
         </is>
       </c>
-      <c r="S90" s="2" t="inlineStr"/>
+      <c r="S90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7459,7 +7544,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. Нужна проверка человеком.</t>
+          <t>Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. На странице указан автор: ИИ Текст. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S93" t="inlineStr"/>
@@ -7848,79 +7933,79 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>https://wav-library.net/sovremennaia-proza/cena-proshheniia</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>wav-library.net</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H99" s="3" t="inlineStr">
         <is>
           <t>Авее Лав</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>Ценадоверия</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K99" s="3" t="inlineStr">
         <is>
           <t>wav-library.net/sovremennaia-proza/cena-proshheniia</t>
         </is>
       </c>
-      <c r="L99" s="2" t="inlineStr">
+      <c r="L99" s="3" t="inlineStr">
         <is>
           <t>Bffdbc8</t>
         </is>
       </c>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="n">
+      <c r="M99" s="3" t="inlineStr"/>
+      <c r="N99" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O99" s="2" t="inlineStr"/>
-      <c r="P99" s="2" t="inlineStr">
+      <c r="O99" s="3" t="inlineStr"/>
+      <c r="P99" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="n">
+      <c r="Q99" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R99" s="2" t="inlineStr">
+      <c r="R99" s="3" t="inlineStr">
         <is>
           <t>Сайт не ответил (SSLError).</t>
         </is>
       </c>
-      <c r="S99" s="2" t="inlineStr"/>
+      <c r="S99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8075,83 +8160,83 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="3" t="n">
         <v>102</v>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>Алекс Мара</t>
         </is>
       </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Разведенаипрекрасна</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>https://free-kniga.ru/yumor/razvedena-i-prekrasna-379393/</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>Алекс Мара</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>Разведенаипрекрасна</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K102" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru/yumor/razvedena-i-prekrasna-379393</t>
         </is>
       </c>
-      <c r="L102" s="2" t="inlineStr">
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>B92dcc8</t>
         </is>
       </c>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="n">
+      <c r="M102" s="3" t="inlineStr"/>
+      <c r="N102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O102" s="2" t="inlineStr">
+      <c r="O102" s="3" t="inlineStr">
         <is>
           <t>автор записан по-разному: Алекс Мара / Мара Алекс</t>
         </is>
       </c>
-      <c r="P102" s="2" t="inlineStr">
+      <c r="P102" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" s="2" t="inlineStr">
+      <c r="Q102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S102" s="2" t="inlineStr">
+      <c r="S102" s="3" t="inlineStr">
         <is>
           <t>B92dcc8</t>
         </is>
@@ -8843,79 +8928,79 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>Алекс Коган</t>
         </is>
       </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>https://zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>zlib.pub</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>Алекс Коган</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K112" s="3" t="inlineStr">
         <is>
           <t>zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
         </is>
       </c>
-      <c r="L112" s="2" t="inlineStr">
+      <c r="L112" s="3" t="inlineStr">
         <is>
           <t>Bbec4dd</t>
         </is>
       </c>
-      <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="n">
+      <c r="M112" s="3" t="inlineStr"/>
+      <c r="N112" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="O112" s="2" t="inlineStr"/>
-      <c r="P112" s="2" t="inlineStr">
+      <c r="O112" s="3" t="inlineStr"/>
+      <c r="P112" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 29% слов)</t>
         </is>
       </c>
-      <c r="Q112" s="2" t="n">
+      <c r="Q112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R112" s="2" t="inlineStr">
+      <c r="R112" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
         </is>
       </c>
-      <c r="S112" s="2" t="inlineStr"/>
+      <c r="S112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -9210,79 +9295,79 @@
       <c r="S116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>Алекс Крамер</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>https://zoboko.com/book/rm9vg3d3/</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>zoboko.com</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>Алекс Крамер</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr">
         <is>
           <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="K117" s="3" t="inlineStr">
         <is>
           <t>zoboko.com/book/rm9vg3d3</t>
         </is>
       </c>
-      <c r="L117" s="2" t="inlineStr">
+      <c r="L117" s="3" t="inlineStr">
         <is>
           <t>Bd7dc3e</t>
         </is>
       </c>
-      <c r="M117" s="2" t="inlineStr"/>
-      <c r="N117" s="2" t="n">
+      <c r="M117" s="3" t="inlineStr"/>
+      <c r="N117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O117" s="2" t="inlineStr"/>
-      <c r="P117" s="2" t="inlineStr">
+      <c r="O117" s="3" t="inlineStr"/>
+      <c r="P117" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R117" s="2" t="inlineStr">
+      <c r="Q117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R117" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S117" s="2" t="inlineStr">
+      <c r="S117" s="3" t="inlineStr">
         <is>
           <t>Bd7dc3e</t>
         </is>
@@ -9368,83 +9453,83 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>Алекс Мара</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Разведенаипрекрасна</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>https://readtoday.ru/yumor/razvedena-i-prekrasna-727057/</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>readtoday.ru</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>Алекс Мара</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr">
         <is>
           <t>Разведенаипрекрасна</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K119" s="3" t="inlineStr">
         <is>
           <t>readtoday.ru/yumor/razvedena-i-prekrasna-727057</t>
         </is>
       </c>
-      <c r="L119" s="2" t="inlineStr">
+      <c r="L119" s="3" t="inlineStr">
         <is>
           <t>B92dcc8</t>
         </is>
       </c>
-      <c r="M119" s="2" t="inlineStr"/>
-      <c r="N119" s="2" t="n">
+      <c r="M119" s="3" t="inlineStr"/>
+      <c r="N119" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="O119" s="2" t="inlineStr">
+      <c r="O119" s="3" t="inlineStr">
         <is>
           <t>автор записан по-разному: Алекс Мара / Мара Алекс</t>
         </is>
       </c>
-      <c r="P119" s="2" t="inlineStr">
+      <c r="P119" s="3" t="inlineStr">
         <is>
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q119" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R119" s="2" t="inlineStr">
+      <c r="Q119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R119" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S119" s="2" t="inlineStr">
+      <c r="S119" s="3" t="inlineStr">
         <is>
           <t>B92dcc8</t>
         </is>
@@ -9885,158 +9970,158 @@
       <c r="S125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
         <is>
           <t>Оксана Алексаева</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>https://booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>booksfb2.com</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>Оксана Алексаева</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="K126" s="3" t="inlineStr">
         <is>
           <t>booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="L126" s="2" t="inlineStr">
+      <c r="L126" s="3" t="inlineStr">
         <is>
           <t>B0930d2</t>
         </is>
       </c>
-      <c r="M126" s="2" t="inlineStr"/>
-      <c r="N126" s="2" t="n">
+      <c r="M126" s="3" t="inlineStr"/>
+      <c r="N126" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O126" s="2" t="inlineStr"/>
-      <c r="P126" s="2" t="inlineStr">
+      <c r="O126" s="3" t="inlineStr"/>
+      <c r="P126" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
         </is>
       </c>
-      <c r="Q126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R126" s="2" t="inlineStr">
+      <c r="Q126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R126" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S126" s="2" t="inlineStr">
+      <c r="S126" s="3" t="inlineStr">
         <is>
           <t>B0930d2</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>Мария Авенская</t>
         </is>
       </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>knigi.fun</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>Мария Авенская</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="K127" s="3" t="inlineStr">
         <is>
           <t>knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
         </is>
       </c>
-      <c r="L127" s="2" t="inlineStr">
+      <c r="L127" s="3" t="inlineStr">
         <is>
           <t>B1686ac</t>
         </is>
       </c>
-      <c r="M127" s="2" t="inlineStr"/>
-      <c r="N127" s="2" t="n">
+      <c r="M127" s="3" t="inlineStr"/>
+      <c r="N127" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O127" s="2" t="inlineStr"/>
-      <c r="P127" s="2" t="inlineStr">
+      <c r="O127" s="3" t="inlineStr"/>
+      <c r="P127" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
         </is>
       </c>
-      <c r="Q127" s="2" t="n">
+      <c r="Q127" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R127" s="2" t="inlineStr">
-        <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
+      <c r="R127" s="3" t="inlineStr">
+        <is>
+          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10827,79 +10912,79 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>Арина Салай</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>https://wav-library.net/proza/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>wav-library.net</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>Арина Салай</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr"/>
+      <c r="J138" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K138" s="3" t="inlineStr">
         <is>
           <t>wav-library.net/proza/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="L138" s="2" t="inlineStr">
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>B81134e</t>
         </is>
       </c>
-      <c r="M138" s="2" t="inlineStr"/>
-      <c r="N138" s="2" t="n">
+      <c r="M138" s="3" t="inlineStr"/>
+      <c r="N138" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O138" s="2" t="inlineStr"/>
-      <c r="P138" s="2" t="inlineStr">
+      <c r="O138" s="3" t="inlineStr"/>
+      <c r="P138" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
         </is>
       </c>
-      <c r="Q138" s="2" t="n">
+      <c r="Q138" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R138" s="2" t="inlineStr">
+      <c r="R138" s="3" t="inlineStr">
         <is>
           <t>Сайт не ответил (SSLError).</t>
         </is>
       </c>
-      <c r="S138" s="2" t="inlineStr"/>
+      <c r="S138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -11129,85 +11214,85 @@
       <c r="S141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>Мария Авенская</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>knigi.fun</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>Мария Авенская</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr"/>
+      <c r="J142" s="3" t="inlineStr">
         <is>
           <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
+      <c r="K142" s="3" t="inlineStr">
         <is>
           <t>knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
         </is>
       </c>
-      <c r="L142" s="2" t="inlineStr">
+      <c r="L142" s="3" t="inlineStr">
         <is>
           <t>B1686ac</t>
         </is>
       </c>
-      <c r="M142" s="2" t="n">
+      <c r="M142" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="N142" s="2" t="n">
+      <c r="N142" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O142" s="2" t="inlineStr">
+      <c r="O142" s="3" t="inlineStr">
         <is>
           <t>дубль строки 127</t>
         </is>
       </c>
-      <c r="P142" s="2" t="inlineStr">
+      <c r="P142" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
         </is>
       </c>
-      <c r="Q142" s="2" t="n">
+      <c r="Q142" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="R142" s="2" t="inlineStr">
-        <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S142" s="2" t="inlineStr"/>
+      <c r="R142" s="3" t="inlineStr">
+        <is>
+          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11366,162 +11451,162 @@
       <c r="S144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B145" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C145" s="3" t="inlineStr">
         <is>
           <t>Полина Рей</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>https://pro-books.ru/proza/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>pro-books.ru</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>Полина Рей</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr">
         <is>
           <t>Измена. Я вас верну</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="K145" s="3" t="inlineStr">
         <is>
           <t>pro-books.ru/proza/izmena-ia-vas-vernu</t>
         </is>
       </c>
-      <c r="L145" s="2" t="inlineStr">
+      <c r="L145" s="3" t="inlineStr">
         <is>
           <t>B1397d8</t>
         </is>
       </c>
-      <c r="M145" s="2" t="inlineStr"/>
-      <c r="N145" s="2" t="n">
+      <c r="M145" s="3" t="inlineStr"/>
+      <c r="N145" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O145" s="2" t="inlineStr"/>
-      <c r="P145" s="2" t="inlineStr">
+      <c r="O145" s="3" t="inlineStr"/>
+      <c r="P145" s="3" t="inlineStr">
         <is>
           <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
         </is>
       </c>
-      <c r="Q145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R145" s="2" t="inlineStr">
+      <c r="Q145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R145" s="3" t="inlineStr">
         <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
         </is>
       </c>
-      <c r="S145" s="2" t="inlineStr">
+      <c r="S145" s="3" t="inlineStr">
         <is>
           <t>B0930d2</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t>Литрес</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>Рудин Алекс</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Егерь-2: Назад в СССР</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>ebook</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>https://free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853/</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>Рудин Алекс</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr"/>
+      <c r="J146" s="3" t="inlineStr">
         <is>
           <t>Егерь-2: Назад в СССР</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
+      <c r="K146" s="3" t="inlineStr">
         <is>
           <t>free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853</t>
         </is>
       </c>
-      <c r="L146" s="2" t="inlineStr">
+      <c r="L146" s="3" t="inlineStr">
         <is>
           <t>Be21c20</t>
         </is>
       </c>
-      <c r="M146" s="2" t="inlineStr"/>
-      <c r="N146" s="2" t="n">
+      <c r="M146" s="3" t="inlineStr"/>
+      <c r="N146" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="O146" s="2" t="inlineStr">
+      <c r="O146" s="3" t="inlineStr">
         <is>
           <t>автор записан по-разному: Алекс Рудин / Рудин Алекс</t>
         </is>
       </c>
-      <c r="P146" s="2" t="inlineStr">
+      <c r="P146" s="3" t="inlineStr">
         <is>
           <t>номер тома или части в адресе другой: в названии 2</t>
         </is>
       </c>
-      <c r="Q146" s="2" t="n">
+      <c r="Q146" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R146" s="2" t="inlineStr">
+      <c r="R146" s="3" t="inlineStr">
         <is>
           <t>Книг из каталога на странице нет. Страница про: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
         </is>
       </c>
-      <c r="S146" s="2" t="inlineStr"/>
+      <c r="S146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11900,7 +11985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11921,47 +12006,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID книги</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Автор</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Строк</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Разных страниц</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Строки в исходнике</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Варианты записи автора</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Варианты названия</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Сайты</t>
         </is>
@@ -15158,7 +15243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15176,32 +15261,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Строка</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Дубль строки</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Автор</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Почему дубль</t>
         </is>
@@ -15685,1545 +15770,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:F18"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Строка</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Автор</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Название</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Что не так по данным</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Что показала страница</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Disciplimit</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Armine Grigoryan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ставка на любовь</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Findroid</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Гнев Империи. Книга 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ася Исай</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Измена. Хочу твоего мужа</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://kniganet.ru/romani/izmena-hochu-tvoego-muzha/</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>17</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Helga D.B.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Анталион</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://librain.ru/boevik/antalion-mest</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>возможно, тот же автор, что Helga Duran</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>26</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Disciplimit</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>31</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ira Kiba</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Кармические узлы в натальной карте</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Кармическая астрология | Книги по кармической астрологии</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>33</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jana Denole Яна Деноль</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Gaunerinnen</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://read.xbook.life/books_gaunerinnen_67131402</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>в поле автора два написания, латиницей и кириллицей</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>35</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Armine Grigoryan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ставка на любовь</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>43</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Lanpirot</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2/</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>номер тома или части в адресе другой: в названии 6</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>на странице другая книга: Lanpirot. Позывной «Хоттабыч»#7. Аватар "Х" (ч.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>46</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Lanpirot</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Позывной «Хоттабыч»#9. Исчадие Кромки (ч. 2)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>https://readtoday.ru/priklyucheniya/pozyvnoy-hottabych-9-ischadie-kromki-ch-2/</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>47</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Larisa Lubimova</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 39% слов)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы. Часть 2: читать и скачать онлайн бесп</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>48</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Елена Полярная</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>https://librain.ru/index.php/detektivy/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>51</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Lilit Khachinyan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Guide de préparation à la production orale du DELF B2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2/</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 40% слов)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Préparation à l’examen du DELF B2 – Language Learning</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>52</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Lost In Space</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Наследник, которого не должно быть</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>https://mp3deer.cc/mp3/%D1%81%D1%83%D0%BF%D0%B5%D1%80-%D0%B0%D1%83%D0%B4%D0%B8%D0%BE%D0%BA%D0%BD%D0%B8%D0%B3%D0%B0-%D0%BD%D0%B0%D1%81%D0%BB%D0%B5%D0%B4%D0%BD%D0%B8%D0%BA-%D0%BA%D0%BE%D1%82%D0%BE%D1%80%D0%BE%D0%B3%D0%BE-%D0%BD%D0%B5-%D0%B4%D0%BE%D0%BB%D0%B6%D0%BD%D0%BE-%D0%B1%D1%8B%D1%82%D1%8C</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>53</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Lucy Zen</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Автономия</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>https://skladmk.online/product/energiya-zhizni-lucy-zen/</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 200, Ошибка | Не удается получить доступ к сайту.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>56</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ravenna</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Бракованный джинн</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>57</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>MILA NENKA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>https://2ivdel.tvoysadik.ru/?section_id=98</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Занимательные раскраски</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>58</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Mind Wave</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Левитация. Путь к внутренней свободе</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://mx-style.net/product/levitacziya-put-k-vnutrennej-svobode-mind-wave/</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Ошибка | Не удается получить доступ к сайту.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>61</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Nika Nika</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Кето-рецепты</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>https://librain.ru/zdorove/keto-recepty</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Кето-рецепты" совпало, но автора из каталога (Nika Nika) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>62</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Nina BROD</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Тишина</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://aknigi24.com/book/tisina-spokoistvie-v-mire-polnom-suma-tit-nat-xan-nikosho</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Тишина" совпало, но автора из каталога (Nina BROD) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>64</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Findroid</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Гнев Империи. Книга 1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>65</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ominayashi</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Пять звезд. Часть 5</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://knigi.ebooker.online/book/42876144-kniga-pyat-zvezd.-chast-5</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>67</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Quartz Y</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Переход в 5D измерение. Просветление. Методичка</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 25% слов)</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полност</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>68</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Rais Ais Gu</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854/</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>74</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Ravenna</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Бракованный джинн</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>75</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Констебль. Том III</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>76</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ravenna</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Медовичок</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>https://litbox.pro/tag/ravenna/</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>на странице другая книга: Ravenna. (Не)зачёт для птички</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>77</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Ravenna</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Медовичок</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://litseries.ru/romany/medovichok-533516/</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>78</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Галина Колоскова</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Измена. Хочу твоего мужа</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>79</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Ravenna</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Медовичок</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://pro-books.ru/liubovnye-romany/medovicok</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>80</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ravenna</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Медовичок</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://readtoday.ru/romany/medovichok-311872/</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>82</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Констебль. Том III</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>87</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/romany/tsena-proscheniya-147884/</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>88</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>https://gigabooks.ru/romany/tsena-proscheniya-686299/</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>89</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>90</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://litseries.ru/romany/tsena-proscheniya-203253/</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>93</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/boevik/cena-doveriia/</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>99</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://wav-library.net/sovremennaia-proza/cena-proshheniia</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>101</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Алекс Ключевской</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Тёмный маг. Книга 1. Неведомый путь</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://knigoline.ru/tyomnyy-mag-kniga-1-nevedomyy-put-4375/</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Своих файлов нет, скачивание и чтение ведут на покупку в Литрес.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>102</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Алекс Мара</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Разведенаипрекрасна</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/yumor/razvedena-i-prekrasna-379393/</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>107</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Алекс Коган</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>https://bibliophile.top/index.php?threads/11672/</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>109</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Алекс Ключевской</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>13-й демон Асмодея. Том 2</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>https://knigoline.ru/13-y-demon-asmodeya-tom-2-9093/</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Своих файлов нет, скачивание и чтение ведут на покупку в Литрес.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>112</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Алекс Коган</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>https://zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 29% слов)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>117</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Алекс Крамер</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://zoboko.com/book/rm9vg3d3/</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>119</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Алекс Мара</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Разведенаипрекрасна</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://readtoday.ru/yumor/razvedena-i-prekrasna-727057/</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>126</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Оксана Алексаева</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>127</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Мария Авенская</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Измена. Хочу твоего мужа</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>138</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Арина Салай</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://wav-library.net/proza/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>139</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Дари Адриана</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Хозяйка таверны "У Черных скал"</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://readtoday.ru/priklyucheniya/oklevetannaya-zhena-drakona-hozyayka-taverny-u-chernyh-skal-945787/</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>142</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Мария Авенская</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Измена. Хочу твоего мужа</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>145</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Полина Рей</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://pro-books.ru/proza/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>146</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Рудин Алекс</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Егерь-2: Назад в СССР</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853/</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>номер тома или части в адресе другой: в названии 2</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>147</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Егорова Надежда</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ночь на Лысой горе. Где забытые боги слышат</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://lllit.ru/ezoterika/noc-na-lysoi-gore-gde-zabytye-bogi-slysat</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: редирект на главную.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17234,7 +15780,1822 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:G55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Строка</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Автор</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Что не так по данным</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Что показала страница</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Каких данных не хватает</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Disciplimit</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Armine Grigoryan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ставка на любовь</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Findroid</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Гнев Империи. Книга 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>на какие форматы есть права: текст, аудио</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ася Исай</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://kniganet.ru/romani/izmena-hochu-tvoego-muzha/</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Helga D.B.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Анталион</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://librain.ru/boevik/antalion-mest</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>возможно, тот же автор, что Helga Duran</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>список псевдонимов и вариантов имени автора</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Disciplimit</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ira Kiba</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Кармические узлы в натальной карте</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Кармическая астрология | Книги по кармической астрологии</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jana Denole Яна Деноль</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Gaunerinnen</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://read.xbook.life/books_gaunerinnen_67131402</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>в поле автора два написания, латиницей и кириллицей</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>основное имя автора и варианты написания</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>35</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Armine Grigoryan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ставка на любовь</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>43</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Lanpirot</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2/</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>номер тома или части в адресе другой: в названии 6</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>на странице другая книга: Lanpirot. Позывной «Хоттабыч»#7. Аватар "Х" (ч.2)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>серия и номер тома отдельными полями; подтверждение правообладателя, к какой книге относится ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>46</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Lanpirot</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Позывной «Хоттабыч»#9. Исчадие Кромки (ч. 2)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://readtoday.ru/priklyucheniya/pozyvnoy-hottabych-9-ischadie-kromki-ch-2/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Larisa Lubimova</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 39% слов)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы. Часть 2: читать и скачать онлайн бесп</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>48</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Елена Полярная</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://librain.ru/index.php/detektivy/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; подтверждение правообладателя, к какой книге относится ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>51</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lilit Khachinyan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Guide de préparation à la production orale du DELF B2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2/</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 40% слов)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Préparation à l’examen du DELF B2 – Language Learning</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>52</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lost In Space</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Наследник, которого не должно быть</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://mp3deer.cc/mp3/%D1%81%D1%83%D0%BF%D0%B5%D1%80-%D0%B0%D1%83%D0%B4%D0%B8%D0%BE%D0%BA%D0%BD%D0%B8%D0%B3%D0%B0-%D0%BD%D0%B0%D1%81%D0%BB%D0%B5%D0%B4%D0%BD%D0%B8%D0%BA-%D0%BA%D0%BE%D1%82%D0%BE%D1%80%D0%BE%D0%B3%D0%BE-%D0%BD%D0%B5-%D0%B4%D0%BE%D0%BB%D0%B6%D0%BD%D0%BE-%D0%B1%D1%8B%D1%82%D1%8C</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>на какие форматы есть права: текст, аудио</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>53</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lucy Zen</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Автономия</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://skladmk.online/product/energiya-zhizni-lucy-zen/</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 200, Ошибка | Не удается получить доступ к сайту.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; не нужны: страница удалена, ссылку можно закрыть</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>56</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Бракованный джинн</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Julia Shi. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>57</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MILA NENKA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://2ivdel.tvoysadik.ru/?section_id=98</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Занимательные раскраски</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>58</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mind Wave</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Левитация. Путь к внутренней свободе</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://mx-style.net/product/levitacziya-put-k-vnutrennej-svobode-mind-wave/</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Ошибка | Не удается получить доступ к сайту.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>61</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nika Nika</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Кето-рецепты</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://librain.ru/zdorove/keto-recepty</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Кето-рецепты" совпало, но автора из каталога (Nika Nika) на странице нет. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>62</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nina BROD</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Тишина</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://aknigi24.com/book/tisina-spokoistvie-v-mire-polnom-suma-tit-nat-xan-nikosho</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Тишина" совпало, но автора из каталога (Nina BROD) на странице нет. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>64</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Findroid</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Гнев Империи. Книга 1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>на какие форматы есть права: текст, аудио</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>65</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ominayashi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Пять звезд. Часть 5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://knigi.ebooker.online/book/42876144-kniga-pyat-zvezd.-chast-5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>не нужны: размещения нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>67</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Quartz Y</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Переход в 5D измерение. Просветление. Методичка</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 25% слов)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полност</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>68</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Rais Ais Gu</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>74</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Бракованный джинн</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Julia Shi. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>75</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Констебль. Том III</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>76</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Медовичок</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://litbox.pro/tag/ravenna/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>на странице другая книга: Ravenna. (Не)зачёт для птички</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; подтверждение правообладателя, к какой книге относится ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>77</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Медовичок</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://litseries.ru/romany/medovichok-533516/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>78</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Галина Колоскова</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>79</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Медовичок</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://pro-books.ru/liubovnye-romany/medovicok</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>80</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ravenna</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Медовичок</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://readtoday.ru/romany/medovichok-311872/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>82</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Констебль. Том III</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>87</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Авее Лав</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://free-kniga.ru/romany/tsena-proscheniya-147884/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>88</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Авее Лав</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://gigabooks.ru/romany/tsena-proscheniya-686299/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>89</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Авее Лав</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>90</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Авее Лав</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://litseries.ru/romany/tsena-proscheniya-203253/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>93</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Авее Лав</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://free-kniga.ru/boevik/cena-doveriia/</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. На странице указан автор: ИИ Текст. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>99</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Авее Лав</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://wav-library.net/sovremennaia-proza/cena-proshheniia</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>101</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Алекс Ключевской</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Тёмный маг. Книга 1. Неведомый путь</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://knigoline.ru/tyomnyy-mag-kniga-1-nevedomyy-put-4375/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Своих файлов нет, скачивание и чтение ведут на покупку в Литрес.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>не нужны: страница партнёрская</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>102</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Алекс Мара</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Разведенаипрекрасна</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://free-kniga.ru/yumor/razvedena-i-prekrasna-379393/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>107</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Алекс Коган</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://bibliophile.top/index.php?threads/11672/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>не нужны: размещения нет</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>109</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Алекс Ключевской</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>13-й демон Асмодея. Том 2</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://knigoline.ru/13-y-demon-asmodeya-tom-2-9093/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Своих файлов нет, скачивание и чтение ведут на покупку в Литрес.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>не нужны: страница партнёрская</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>112</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Алекс Коган</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 29% слов)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>117</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Алекс Крамер</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://zoboko.com/book/rm9vg3d3/</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>119</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Алекс Мара</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Разведенаипрекрасна</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://readtoday.ru/yumor/razvedena-i-prekrasna-727057/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Оксана Алексаева</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Мария Авенская</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>138</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Арина Салай</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://wav-library.net/proza/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>139</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Дари Адриана</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Хозяйка таверны "У Черных скал"</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://readtoday.ru/priklyucheniya/oklevetannaya-zhena-drakona-hozyayka-taverny-u-chernyh-skal-945787/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>142</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Мария Авенская</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>145</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Полина Рей</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://pro-books.ru/proza/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; подтверждение правообладателя, к какой книге относится ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>146</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Рудин Алекс</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Егерь-2: Назад в СССР</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>номер тома или части в адресе другой: в названии 2</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>серия и номер тома отдельными полями; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>147</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Егорова Надежда</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ночь на Лысой горе. Где забытые боги слышат</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://lllit.ru/ezoterika/noc-na-lysoi-gore-gde-zabytye-bogi-slysat</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: редирект на главную.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G55"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -17245,71 +17606,77 @@
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="35" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Строка в исходнике</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Правообладатель</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Автор</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Тип контента</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Сайт</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Пират-1/не пират-0 (статус 0/1/2)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Признаки</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ответ сайта</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Что на странице</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Книга на странице</t>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Статус страницы</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Извлечённые данные</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Совпадение с каталогом</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Причина решения</t>
         </is>
       </c>
     </row>
@@ -17352,22 +17719,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>аудио, слушать онлайн; это аудиоверсия</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>заголовок: Аудиокнига Цветок в мужской академии магии, Наталья Буланова (читает Татьяна Черничкина) – слушать или скачать онлайн; автор на странице: Наталья Буланова</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Наталья Буланова. Цветок в мужской академии магии</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: это аудиоверсия; аудио, слушать онлайн.</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Аудиокнига Цветок в мужской академии магии, Наталья Буланова (читает Татьяна Черничкина) – слушать или скачать онлайн</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Наталья Буланова. Цветок в мужской академии магии</t>
         </is>
       </c>
     </row>
@@ -17410,20 +17782,29 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>файл PDF на 265 стр.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>заголовок: Разреши любить. Позволь мне быть рядом. Книга 2 Анна Джейн; тип: application/pdf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>Книг из каталога на странице нет. Страница про: Разреши любить. Позволь мне быть рядом. Книга 2 Анна Джейн</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Разреши любить. Позволь мне быть рядом. Книга 2 Анна Джейн</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -17464,22 +17845,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>текст книги прямо на странице</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>заголовок: Системный разведчик. Инфильтрация. Дилогия, Юрич Валерий - читать онлайн без регистрации</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Юрич Валерий. Системный разведчик. Инфильтрация. Дилогия</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: текст книги прямо на странице.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Системный разведчик. Инфильтрация. Дилогия, Юрич Валерий - читать онлайн без регистрации</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Юрич Валерий. Системный разведчик. Инфильтрация. Дилогия</t>
         </is>
       </c>
     </row>
@@ -17522,22 +17908,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>торрент; кнопка скачивания; это аудиоверсия</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>заголовок: Тайновидец. Том 13: Мастер невезения - Рудин Алекс аудиокнига торрент mp3 | Тайновидец. Том 13: Мастер невезения — Рудин Алекс; автор на странице: Рудин Алекс</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Алекс Рудин. Тайновидец. Том 13: Мастер невезения</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: это аудиоверсия; торрент; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Тайновидец. Том 13: Мастер невезения - Рудин Алекс аудиокнига торрент mp3 | Тайновидец. Том 13: Мастер невезения — Рудин Алекс</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Алекс Рудин. Тайновидец. Том 13: Мастер невезения</t>
         </is>
       </c>
     </row>
@@ -17580,22 +17971,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>кнопка скачивания; скачивание zip; файлообменники htfl.net, nitroflare.com, trbt.cc</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>заголовок: Евгений Нетт - Сборник произведений (полная версия) скачать бесплатно | Евгений Нетт - Сборник произведений скачать бесплатно</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Евгений Нетт. Директива: Сохранить!</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>Книга найдена в тексте страницы (сборник или список), автор совпал. Признаки размещения: скачивание zip; файлообменники htfl.net, nitroflare.com, trbt.cc; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Евгений Нетт - Сборник произведений (полная версия) скачать бесплатно | Евгений Нетт - Сборник произведений скачать бесплатно</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Евгений Нетт. Директива: Сохранить!</t>
         </is>
       </c>
     </row>
@@ -17638,22 +18034,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>чтение онлайн; скачивание epub, fb2, txt</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>заголовок: Замуж по договору Татьяна Серганова — читать онлайн или скачать бесплатно; автор на странице: Татьяна Серганова</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Татьяна Серганова. Замуж по договору</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Замуж по договору Татьяна Серганова — читать онлайн или скачать бесплатно</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Татьяна Серганова. Замуж по договору</t>
         </is>
       </c>
     </row>
@@ -17696,22 +18097,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>кнопка скачивания; чтение онлайн; ссылки на покупку в Литрес</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>заголовок: Ярость Вечных: скачать fb2, epub, pdf, txt | Антон Карелин; автор на странице: Антон Карелин</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Антон Карелин. Ярость Вечных</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>Книга найдена в заголовке, автор совпал. Своих файлов нет, скачивание и чтение ведут на покупку в Литрес.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Ярость Вечных: скачать fb2, epub, pdf, txt | Антон Карелин</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Антон Карелин. Ярость Вечных</t>
         </is>
       </c>
     </row>
@@ -17754,22 +18160,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>чтение онлайн; кнопка скачивания; скачивание epub, fb2, txt</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>заголовок: Ярроу: читать и скачать онлайн бесплатно полностью fb2; автор на странице: Вторая</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Айлин Лин. Ярроу</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Ярроу: читать и скачать онлайн бесплатно полностью fb2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Айлин Лин. Ярроу</t>
         </is>
       </c>
     </row>
@@ -17812,22 +18223,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>текст книги прямо на странице</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>200, ok</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>заголовок: Ясновидеть может каждый или как развить в себе сверхспособности, Хайр Хелен, книга полностью, читать бесплатно без сокращений</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Хелен Хайр. Ясновидеть может каждый, или Как развить в себе сверхспособности</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>Книга найдена в заголовке, автор совпал. Признаки размещения: текст книги прямо на странице.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Ясновидеть может каждый или как развить в себе сверхспособности, Хайр Хелен, книга полностью, читать бесплатно без сокращений</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Хелен Хайр. Ясновидеть может каждый, или Как развить в себе сверхспособности</t>
         </is>
       </c>
     </row>
@@ -17868,25 +18284,30 @@
       <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>200, нет содержимого</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>заголовок: Загрузка — Библибоба</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>нет содержимого</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Загрузка — Библибоба</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:M11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/out/result.xlsx
+++ b/out/result.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Дубли" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Спорные" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Задание 2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Рекомендации ИИ" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Строки'!$A$1:$S$151</definedName>
@@ -20,6 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Дубли'!$A$1:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спорные'!$A$1:$G$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Задание 2'!$A$1:$M$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Рекомендации ИИ'!$A$1:$D$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18051,7 +18053,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -18065,17 +18067,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>заголовок: Ярость Вечных: скачать fb2, epub, pdf, txt | Антон Карелин; автор на странице: Антон Карелин</t>
+          <t>заголовок: Ярость Вечных: скачать fb2, epub, pdf, txt | Антон Карелин; автор на странице: Антон Карелин; ИИ: решение уточнено, цитаты проверены</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>Антон Карелин. Ярость Вечных</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
+          <t>ИИ-проверка: Есть совпадение названия и автора, но размещение книги не подтверждено: на сайте предлагается лишь покупка платной версии на партнёрском ресурсе.</t>
         </is>
       </c>
     </row>
@@ -18268,4 +18270,207 @@
   <autoFilter ref="A1:M11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Строка в исходнике</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Цитата из строки</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Что проверить (рекомендация ИИ)</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Каких данных не хватает</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>проверьте соответствие адреса страницы названию и автору книги</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>правильный URL страницы товара</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>проверьте формат издания книги и соответствие ссылки</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>тип издания и корректная ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>проверьте формат книги и соответствие ссылки на скачивание или покупку</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>тип издания и корректная ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>проверьте правильность указания авторства для данного названия</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>корректное имя автора</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>проверьте соответствие URL страницы названию книги</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>верный URL страницы</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>в поле автора два написания, латиницей и кириллицей</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>проверьте правильность написания имени автора в соответствии со стандартами каталога</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>основной вариант имени автора</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>номер тома или части в адресе другой: в названии 6</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>проверьте номер тома или части в названии и адресе страницы</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>правильный номер тома</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 39% слов)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>проверьте соответствие адреса страницы названию книги</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>актуальный URL страницы</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/out/result.xlsx
+++ b/out/result.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Дубли'!$A$1:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спорные'!$A$1:$G$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Задание 2'!$A$1:$M$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Рекомендации ИИ'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Рекомендации ИИ'!$A$1:$E$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18278,13 +18278,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18300,12 +18301,17 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Что проверить (рекомендация ИИ)</t>
+          <t>Что проверить</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Каких данных не хватает</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Источник рекомендации</t>
         </is>
       </c>
     </row>
@@ -18315,17 +18321,22 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>проверьте соответствие адреса страницы названию и автору книги</t>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>правильный URL страницы товара</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
@@ -18335,17 +18346,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
+          <t>Ставка на любовь</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>проверьте формат издания книги и соответствие ссылки</t>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>тип издания и корректная ссылка</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
@@ -18355,17 +18371,22 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
+          <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>проверьте формат книги и соответствие ссылки на скачивание или покупку</t>
+          <t>Проверить: тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>тип издания и корректная ссылка</t>
+          <t>на какие форматы есть права: текст, аудио</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
@@ -18375,17 +18396,22 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+          <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>проверьте правильность указания авторства для данного названия</t>
+          <t>Проверить: это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>корректное имя автора</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
@@ -18395,17 +18421,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>Кармические узлы в натальной карте</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>проверьте соответствие URL страницы названию книги</t>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>верный URL страницы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
@@ -18415,17 +18446,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>в поле автора два написания, латиницей и кириллицей</t>
+          <t>Gaunerinnen</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>проверьте правильность написания имени автора в соответствии со стандартами каталога</t>
+          <t>Проверить: в поле автора два написания, латиницей и кириллицей</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>основной вариант имени автора</t>
+          <t>основное имя автора и варианты написания</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
@@ -18435,17 +18471,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>номер тома или части в адресе другой: в названии 6</t>
+          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>проверьте номер тома или части в названии и адресе страницы</t>
+          <t>Проверить: номер тома или части в адресе другой: в названии 6</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>правильный номер тома</t>
+          <t>серия и номер тома отдельными полями</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
@@ -18455,22 +18496,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 39% слов)</t>
+          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>проверьте соответствие адреса страницы названию книги</t>
+          <t>Проверить: адрес страницы не похож на название (совпало 39% слов)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>актуальный URL страницы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
+  <autoFilter ref="A1:E9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/out/result.xlsx
+++ b/out/result.xlsx
@@ -18321,22 +18321,22 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>Проверить, что ссылка ведёт на эту книгу, а не на другой товар</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>Полный URL и подтверждение названия со страницы</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18346,22 +18346,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Ставка на любовь</t>
+          <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Проверить: адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
+          <t>Уточнить формат издания и соответствует ли ссылка ему</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
+          <t>Полный URL, формат и обложка или описание страницы</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18371,22 +18371,22 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Гнев Империи. Книга 1</t>
+          <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Проверить: тип ebook, а ссылка похожа на аудио</t>
+          <t>Сверить формат с типом записи перед публикацией</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>на какие форматы есть права: текст, аудио</t>
+          <t>Полный URL и явное указание формата</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18396,22 +18396,22 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Измена. Хочу твоего мужа</t>
+          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Проверить: это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+          <t>Проверить автора и издание, не сливать книги разных авторов</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+          <t>ISBN или издательские данные для каждой версии</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18421,22 +18421,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Кармические узлы в натальной карте</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>Проверить соответствие ссылки названию и автору</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>Полный URL и название со страницы</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18446,22 +18446,22 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Gaunerinnen</t>
+          <t>в поле автора два написания, латиницей и кириллицей</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Проверить: в поле автора два написания, латиницей и кириллицей</t>
+          <t>Уточнить, это один автор или псевдоним, не склеивать записи</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>основное имя автора и варианты написания</t>
+          <t>Ссылка на профиль автора и подтверждение написания</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18471,22 +18471,22 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
+          <t>номер тома или части в адресе другой: в названии 6</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Проверить: номер тома или части в адресе другой: в названии 6</t>
+          <t>Проверить номер тома в названии и на странице издания</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>серия и номер тома отдельными полями</t>
+          <t>Полный URL и номер тома с обложки</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18496,22 +18496,22 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
+          <t>адрес страницы не похож на название (совпало 39% слов)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Проверить: адрес страницы не похож на название (совпало 39% слов)</t>
+          <t>Сверить ссылку и слишком длинное название, возможно это сборник</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>Полный URL и структура названия из источника</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Правила: превышено время ожидания ИИ</t>
+          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
         </is>
       </c>
     </row>

--- a/out/result.xlsx
+++ b/out/result.xlsx
@@ -19,9 +19,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Строки'!$A$1:$S$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Книги'!$A$1:$I$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Дубли'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спорные'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спорные'!$A$1:$G$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Задание 2'!$A$1:$M$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Рекомендации ИИ'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Рекомендации ИИ'!$A$1:$E$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -718,7 +718,7 @@
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -793,7 +793,7 @@
       </c>
       <c r="R3" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S3" s="4" t="inlineStr"/>
@@ -860,14 +860,18 @@
       <c r="O4" s="4" t="inlineStr"/>
       <c r="P4" s="4" t="inlineStr"/>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>B5d524b</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="4" t="n">
@@ -931,18 +935,14 @@
       <c r="O5" s="4" t="inlineStr"/>
       <c r="P5" s="4" t="inlineStr"/>
       <c r="Q5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>B5d524b</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr"/>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr"/>
@@ -1610,11 +1610,11 @@
         </is>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
+          <t>ИИ-проверка: Название совпадает, но указанный на странице автор Оксана Алексаева отсутствует среди кандидатов.</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -1831,18 +1831,14 @@
       <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" s="4" t="inlineStr"/>
       <c r="Q17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>B9bae6e</t>
-        </is>
-      </c>
+          <t>Сайт не ответил (Timeout).</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -2066,7 +2062,7 @@
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S20" s="4" t="inlineStr"/>
@@ -2522,7 +2518,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -2593,7 +2589,7 @@
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
+          <t>ИИ-проверка: Название и автор (Хельга Дюран / Helga Duran) совпадают с каталогом, книга размещена с возможностью скачивания.</t>
         </is>
       </c>
       <c r="S27" s="4" t="inlineStr">
@@ -2739,18 +2735,14 @@
       <c r="O29" s="4" t="inlineStr"/>
       <c r="P29" s="4" t="inlineStr"/>
       <c r="Q29" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S29" s="4" t="inlineStr">
-        <is>
-          <t>B584abb</t>
-        </is>
-      </c>
+          <t>Название "Тарский горячий твой" совпало, но автора из каталога (Helga Duran) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr"/>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="4" t="n">
@@ -2897,7 +2889,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Кармическая астрология | Книги по кармической астрологии</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Кармическая астрология | Книги по кармической астрологии</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -3122,7 +3114,7 @@
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S34" s="4" t="inlineStr"/>
@@ -3345,18 +3337,14 @@
       <c r="O37" s="4" t="inlineStr"/>
       <c r="P37" s="4" t="inlineStr"/>
       <c r="Q37" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S37" s="4" t="inlineStr">
-        <is>
-          <t>Bd7871a</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr"/>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="4" t="n">
@@ -3424,7 +3412,7 @@
       </c>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S38" s="4" t="inlineStr"/>
@@ -4099,11 +4087,11 @@
         </is>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы. Часть 2: читать и скачать онлайн бесп</t>
+          <t>Сайт не ответил (Timeout).</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
@@ -4174,18 +4162,14 @@
         </is>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S48" s="3" t="inlineStr">
-        <is>
-          <t>B0930d2</t>
-        </is>
-      </c>
+          <t>Сайт не ответил (Timeout).</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="4" t="n">
@@ -4405,7 +4389,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Préparation à l’examen du DELF B2 – Language Learning</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Préparation à l’examen du DELF B2 – Language Learning</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
@@ -4551,11 +4535,11 @@
         </is>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>Страницы нет: ответ 200, Ошибка | Не удается получить доступ к сайту.</t>
+          <t>Получена страница ошибки вместо книги. Отсутствие книги не подтверждено, нужна повторная проверка.</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
@@ -4622,18 +4606,14 @@
       <c r="O54" s="4" t="inlineStr"/>
       <c r="P54" s="4" t="inlineStr"/>
       <c r="Q54" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R54" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S54" s="4" t="inlineStr">
-        <is>
-          <t>Be74d3f</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S54" s="4" t="inlineStr"/>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="4" t="n">
@@ -4697,14 +4677,18 @@
       <c r="O55" s="4" t="inlineStr"/>
       <c r="P55" s="4" t="inlineStr"/>
       <c r="Q55" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S55" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S55" s="4" t="inlineStr">
+        <is>
+          <t>Bdaf254</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="4" t="n">
@@ -4772,7 +4756,7 @@
       </c>
       <c r="R56" s="4" t="inlineStr">
         <is>
-          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S56" s="4" t="inlineStr"/>
@@ -4847,7 +4831,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Занимательные раскраски</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Занимательные раскраски</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
@@ -5060,18 +5044,14 @@
       <c r="O60" s="4" t="inlineStr"/>
       <c r="P60" s="4" t="inlineStr"/>
       <c r="Q60" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S60" s="4" t="inlineStr">
-        <is>
-          <t>Be054eb</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="inlineStr"/>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="4" t="n">
@@ -5595,7 +5575,7 @@
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полност</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полностью fb2</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
@@ -5666,14 +5646,18 @@
         </is>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S68" s="3" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr">
+        <is>
+          <t>B4b3214</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="58" customHeight="1">
       <c r="A69" s="4" t="n">
@@ -5737,18 +5721,14 @@
       <c r="O69" s="4" t="inlineStr"/>
       <c r="P69" s="4" t="inlineStr"/>
       <c r="Q69" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R69" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S69" s="4" t="inlineStr">
-        <is>
-          <t>B4b3214</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S69" s="4" t="inlineStr"/>
     </row>
     <row r="70" ht="58" customHeight="1">
       <c r="A70" s="4" t="n">
@@ -5818,14 +5798,18 @@
       </c>
       <c r="P70" s="4" t="inlineStr"/>
       <c r="Q70" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S70" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>Bdaf254</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="58" customHeight="1">
       <c r="A71" s="4" t="n">
@@ -5889,14 +5873,18 @@
       <c r="O71" s="4" t="inlineStr"/>
       <c r="P71" s="4" t="inlineStr"/>
       <c r="Q71" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S71" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S71" s="4" t="inlineStr">
+        <is>
+          <t>B4b3214</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="58" customHeight="1">
       <c r="A72" s="4" t="n">
@@ -5964,7 +5952,7 @@
       </c>
       <c r="R72" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S72" s="4" t="inlineStr"/>
@@ -6031,18 +6019,14 @@
       <c r="O73" s="4" t="inlineStr"/>
       <c r="P73" s="4" t="inlineStr"/>
       <c r="Q73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R73" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S73" s="4" t="inlineStr">
-        <is>
-          <t>B144a58</t>
-        </is>
-      </c>
+          <t>Название "(Не)зачёт для птички" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S73" s="4" t="inlineStr"/>
     </row>
     <row r="74" ht="58" customHeight="1">
       <c r="A74" s="4" t="n">
@@ -6116,7 +6100,7 @@
       </c>
       <c r="R74" s="4" t="inlineStr">
         <is>
-          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="S74" s="4" t="inlineStr"/>
@@ -6270,7 +6254,7 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Книги автора Равенна | LitBox | Равенна - скачать и читать все книги онлайн бесплатно полностью</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Книги автора Равенна | LitBox | Равенна - скачать и читать все книги онлайн бесплатно полностью</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr"/>
@@ -6625,14 +6609,18 @@
       <c r="O81" s="4" t="inlineStr"/>
       <c r="P81" s="4" t="inlineStr"/>
       <c r="Q81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S81" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S81" s="4" t="inlineStr">
+        <is>
+          <t>B8b83ea</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="58" customHeight="1">
       <c r="A82" s="3" t="n">
@@ -6785,18 +6773,14 @@
       </c>
       <c r="P83" s="4" t="inlineStr"/>
       <c r="Q83" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R83" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S83" s="4" t="inlineStr">
-        <is>
-          <t>Bf8c90f</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S83" s="4" t="inlineStr"/>
     </row>
     <row r="84" ht="58" customHeight="1">
       <c r="A84" s="4" t="n">
@@ -6866,14 +6850,18 @@
       </c>
       <c r="P84" s="4" t="inlineStr"/>
       <c r="Q84" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R84" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S84" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S84" s="4" t="inlineStr">
+        <is>
+          <t>B8b83ea</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="58" customHeight="1">
       <c r="A85" s="4" t="n">
@@ -7091,7 +7079,7 @@
       </c>
       <c r="R87" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
         </is>
       </c>
       <c r="S87" s="3" t="inlineStr"/>
@@ -7166,7 +7154,7 @@
       </c>
       <c r="R88" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
         </is>
       </c>
       <c r="S88" s="3" t="inlineStr"/>
@@ -7241,7 +7229,7 @@
       </c>
       <c r="R89" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
         </is>
       </c>
       <c r="S89" s="3" t="inlineStr"/>
@@ -7316,7 +7304,7 @@
       </c>
       <c r="R90" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
         </is>
       </c>
       <c r="S90" s="3" t="inlineStr"/>
@@ -7610,14 +7598,18 @@
       <c r="O94" s="4" t="inlineStr"/>
       <c r="P94" s="4" t="inlineStr"/>
       <c r="Q94" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R94" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S94" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S94" s="4" t="inlineStr">
+        <is>
+          <t>B14dce4</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="58" customHeight="1">
       <c r="A95" s="4" t="n">
@@ -7687,14 +7679,18 @@
       </c>
       <c r="P95" s="4" t="inlineStr"/>
       <c r="Q95" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R95" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S95" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S95" s="4" t="inlineStr">
+        <is>
+          <t>B14dce4</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="58" customHeight="1">
       <c r="A96" s="4" t="n">
@@ -7762,18 +7758,14 @@
       </c>
       <c r="P96" s="4" t="inlineStr"/>
       <c r="Q96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R96" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S96" s="4" t="inlineStr">
-        <is>
-          <t>Ba025f1</t>
-        </is>
-      </c>
+          <t>Название "Хозяйка Солнечного поместья" совпало, но автора из каталога (Адриана Дари) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S96" s="4" t="inlineStr"/>
     </row>
     <row r="97" ht="58" customHeight="1">
       <c r="A97" s="4" t="n">
@@ -7837,18 +7829,14 @@
       <c r="O97" s="4" t="inlineStr"/>
       <c r="P97" s="4" t="inlineStr"/>
       <c r="Q97" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R97" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S97" s="4" t="inlineStr">
-        <is>
-          <t>B2899ff</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S97" s="4" t="inlineStr"/>
     </row>
     <row r="98" ht="58" customHeight="1">
       <c r="A98" s="4" t="n">
@@ -7918,18 +7906,14 @@
       </c>
       <c r="P98" s="4" t="inlineStr"/>
       <c r="Q98" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R98" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S98" s="4" t="inlineStr">
-        <is>
-          <t>B2899ff</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S98" s="4" t="inlineStr"/>
     </row>
     <row r="99" ht="58" customHeight="1">
       <c r="A99" s="3" t="n">
@@ -8303,18 +8287,14 @@
       <c r="O103" s="4" t="inlineStr"/>
       <c r="P103" s="4" t="inlineStr"/>
       <c r="Q103" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R103" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S103" s="4" t="inlineStr">
-        <is>
-          <t>B7dd037</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S103" s="4" t="inlineStr"/>
     </row>
     <row r="104" ht="58" customHeight="1">
       <c r="A104" s="4" t="n">
@@ -8692,7 +8672,7 @@
       </c>
       <c r="R108" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S108" s="4" t="inlineStr"/>
@@ -8842,14 +8822,18 @@
       <c r="O110" s="4" t="inlineStr"/>
       <c r="P110" s="4" t="inlineStr"/>
       <c r="Q110" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R110" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S110" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S110" s="4" t="inlineStr">
+        <is>
+          <t>Bbec4dd</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="58" customHeight="1">
       <c r="A111" s="4" t="n">
@@ -8913,18 +8897,14 @@
       <c r="O111" s="4" t="inlineStr"/>
       <c r="P111" s="4" t="inlineStr"/>
       <c r="Q111" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R111" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S111" s="4" t="inlineStr">
-        <is>
-          <t>Bbec4dd</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S111" s="4" t="inlineStr"/>
     </row>
     <row r="112" ht="58" customHeight="1">
       <c r="A112" s="3" t="n">
@@ -8996,7 +8976,7 @@
       </c>
       <c r="R112" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
         </is>
       </c>
       <c r="S112" s="3" t="inlineStr"/>
@@ -9213,14 +9193,18 @@
       <c r="O115" s="4" t="inlineStr"/>
       <c r="P115" s="4" t="inlineStr"/>
       <c r="Q115" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R115" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S115" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S115" s="4" t="inlineStr">
+        <is>
+          <t>Be7cb4c</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="58" customHeight="1">
       <c r="A116" s="4" t="n">
@@ -9438,18 +9422,14 @@
       </c>
       <c r="P118" s="4" t="inlineStr"/>
       <c r="Q118" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R118" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S118" s="4" t="inlineStr">
-        <is>
-          <t>B6f939c</t>
-        </is>
-      </c>
+          <t>Название "Пухленькая Рыженькая" совпало, но автора из каталога (Алекс Мара) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S118" s="4" t="inlineStr"/>
     </row>
     <row r="119" ht="58" customHeight="1">
       <c r="A119" s="3" t="n">
@@ -9600,7 +9580,7 @@
       </c>
       <c r="R120" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S120" s="4" t="inlineStr"/>
@@ -9667,18 +9647,14 @@
       <c r="O121" s="4" t="inlineStr"/>
       <c r="P121" s="4" t="inlineStr"/>
       <c r="Q121" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R121" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S121" s="4" t="inlineStr">
-        <is>
-          <t>B8b2feb</t>
-        </is>
-      </c>
+          <t>Название "Девственность по контракту" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S121" s="4" t="inlineStr"/>
     </row>
     <row r="122" ht="58" customHeight="1">
       <c r="A122" s="4" t="n">
@@ -9817,7 +9793,7 @@
       </c>
       <c r="R123" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S123" s="4" t="inlineStr"/>
@@ -9884,18 +9860,14 @@
       <c r="O124" s="4" t="inlineStr"/>
       <c r="P124" s="4" t="inlineStr"/>
       <c r="Q124" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R124" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S124" s="4" t="inlineStr">
-        <is>
-          <t>Bc730f2</t>
-        </is>
-      </c>
+          <t>Название "Жена для Синей Бороды" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S124" s="4" t="inlineStr"/>
     </row>
     <row r="125" ht="58" customHeight="1">
       <c r="A125" s="4" t="n">
@@ -9959,11 +9931,11 @@
       <c r="O125" s="4" t="inlineStr"/>
       <c r="P125" s="4" t="inlineStr"/>
       <c r="Q125" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R125" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
         </is>
       </c>
       <c r="S125" s="4" t="inlineStr"/>
@@ -10190,18 +10162,14 @@
       </c>
       <c r="P128" s="4" t="inlineStr"/>
       <c r="Q128" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R128" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S128" s="4" t="inlineStr">
-        <is>
-          <t>B7dd037</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S128" s="4" t="inlineStr"/>
     </row>
     <row r="129" ht="58" customHeight="1">
       <c r="A129" s="4" t="n">
@@ -10427,18 +10395,14 @@
       </c>
       <c r="P131" s="4" t="inlineStr"/>
       <c r="Q131" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R131" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S131" s="4" t="inlineStr">
-        <is>
-          <t>Bce9a30</t>
-        </is>
-      </c>
+          <t>Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S131" s="4" t="inlineStr"/>
     </row>
     <row r="132" ht="58" customHeight="1">
       <c r="A132" s="4" t="n">
@@ -10585,18 +10549,14 @@
       </c>
       <c r="P133" s="4" t="inlineStr"/>
       <c r="Q133" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R133" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S133" s="4" t="inlineStr">
-        <is>
-          <t>Bce9a30</t>
-        </is>
-      </c>
+          <t>Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S133" s="4" t="inlineStr"/>
     </row>
     <row r="134" ht="58" customHeight="1">
       <c r="A134" s="4" t="n">
@@ -10897,18 +10857,14 @@
       <c r="O137" s="4" t="inlineStr"/>
       <c r="P137" s="4" t="inlineStr"/>
       <c r="Q137" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R137" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S137" s="4" t="inlineStr">
-        <is>
-          <t>Bbd74a3</t>
-        </is>
-      </c>
+          <t>Название "Двойное удовольствие" совпало, но автора из каталога (Алекс Хот) на странице нет. На странице указан автор: Mery. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S137" s="4" t="inlineStr"/>
     </row>
     <row r="138" ht="58" customHeight="1">
       <c r="A138" s="3" t="n">
@@ -11122,18 +11078,14 @@
       <c r="O140" s="4" t="inlineStr"/>
       <c r="P140" s="4" t="inlineStr"/>
       <c r="Q140" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R140" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S140" s="4" t="inlineStr">
-        <is>
-          <t>Be7cb4c</t>
-        </is>
-      </c>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
+        </is>
+      </c>
+      <c r="S140" s="4" t="inlineStr"/>
     </row>
     <row r="141" ht="58" customHeight="1">
       <c r="A141" s="4" t="n">
@@ -11203,14 +11155,18 @@
       </c>
       <c r="P141" s="4" t="inlineStr"/>
       <c r="Q141" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R141" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S141" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S141" s="4" t="inlineStr">
+        <is>
+          <t>Be7cb4c</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="58" customHeight="1">
       <c r="A142" s="3" t="n">
@@ -11359,18 +11315,14 @@
       </c>
       <c r="P143" s="4" t="inlineStr"/>
       <c r="Q143" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R143" s="4" t="inlineStr">
         <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S143" s="4" t="inlineStr">
-        <is>
-          <t>B116af7</t>
-        </is>
-      </c>
+          <t>Название "Будь моим бывшим" совпало, но автора из каталога (Мара Алекс) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="S143" s="4" t="inlineStr"/>
     </row>
     <row r="144" ht="58" customHeight="1">
       <c r="A144" s="4" t="n">
@@ -11440,11 +11392,11 @@
       </c>
       <c r="P144" s="4" t="inlineStr"/>
       <c r="Q144" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R144" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
         </is>
       </c>
       <c r="S144" s="4" t="inlineStr"/>
@@ -11602,7 +11554,7 @@
       </c>
       <c r="R146" s="3" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
+          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
         </is>
       </c>
       <c r="S146" s="3" t="inlineStr"/>
@@ -11823,14 +11775,18 @@
       <c r="O149" s="4" t="inlineStr"/>
       <c r="P149" s="4" t="inlineStr"/>
       <c r="Q149" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R149" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
-        </is>
-      </c>
-      <c r="S149" s="4" t="inlineStr"/>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
+        </is>
+      </c>
+      <c r="S149" s="4" t="inlineStr">
+        <is>
+          <t>B3ff35a</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="58" customHeight="1">
       <c r="A150" s="4" t="n">
@@ -11973,7 +11929,7 @@
       </c>
       <c r="R151" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
         </is>
       </c>
       <c r="S151" s="4" t="inlineStr"/>
@@ -15779,7 +15735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15892,555 +15848,539 @@
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Findroid</t>
+          <t>DIGITAL ZEN</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Гнев Империи. Книга 1</t>
+          <t>ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
+          <t>https://skladchik.tv/threads/prompt-suno-com-ehnciklopedija-i-polnoe-rukovodstvo-po-sostavleniju-prompta-ddigital-zen.489299/</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>на какие форматы есть права: текст, аудио</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ася Исай</t>
+          <t>Findroid</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Измена. Хочу твоего мужа</t>
+          <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>https://kniganet.ru/romani/izmena-hochu-tvoego-muzha/</t>
+          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+          <t>на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Disciplimit</t>
+          <t>Ася Исай</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
+          <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
+          <t>https://kniganet.ru/romani/izmena-hochu-tvoego-muzha/</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): ИИ-проверка: Название совпадает, но указанный на странице автор Оксана Алексаева отсутствует среди кандидатов.</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Ira Kiba</t>
+          <t>DIGITAL ZEN</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Кармические узлы в натальной карте</t>
+          <t>ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>https://astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
+          <t>https://s4.skladchik.tv/threads/prompt-suno-com-ehnciklopedija-i-polnoe-rukovodstvo-po-sostavleniju-prompta-ddigital-zen.489299/</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Кармическая астрология | Книги по кармической астрологии</t>
+          <t>страница не подтвердила книгу (статус 2): Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Jana Denole Яна Деноль</t>
+          <t>Disciplimit</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Gaunerinnen</t>
+          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>https://read.xbook.life/books_gaunerinnen_67131402</t>
+          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>в поле автора два написания, латиницей и кириллицей</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>основное имя автора и варианты написания</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Armine Grigoryan</t>
+          <t>Helga Duran</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Ставка на любовь</t>
+          <t>Тарский горячий твой</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
+          <t>https://listaibuk.com/sovremennie-lyubovnie-romani/tarskiy-goryachiy-tvoy/</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Тарский горячий твой" совпало, но автора из каталога (Helga Duran) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Lanpirot</t>
+          <t>Ira Kiba</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
+          <t>Кармические узлы в натальной карте</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>https://free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2/</t>
+          <t>https://astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>номер тома или части в адресе другой: в названии 6</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>на странице другая книга: Lanpirot. Позывной «Хоттабыч»#7. Аватар "Х" (ч.2)</t>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Кармическая астрология | Книги по кармической астрологии</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>серия и номер тома отдельными полями; подтверждение правообладателя, к какой книге относится ссылка</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Lanpirot</t>
+          <t>Jana Denole Яна Деноль</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Позывной «Хоттабыч»#9. Исчадие Кромки (ч. 2)</t>
+          <t>Gaunerinnen</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>https://readtoday.ru/priklyucheniya/pozyvnoy-hottabych-9-ischadie-kromki-ch-2/</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
+          <t>https://read.xbook.life/books_gaunerinnen_67131402</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>в поле автора два написания, латиницей и кириллицей</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+          <t>основное имя автора и варианты написания</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Larisa Lubimova</t>
+          <t>Armine Grigoryan</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
+          <t>Ставка на любовь</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>https://librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
+          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 39% слов)</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы. Часть 2: читать и скачать онлайн бесп</t>
-        </is>
-      </c>
+          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Елена Полярная</t>
+          <t>Lanpirot</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Измена. Я вас верну</t>
+          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>https://librain.ru/index.php/detektivy/izmena-ia-vas-vernu</t>
+          <t>https://free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2/</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
+          <t>номер тома или части в адресе другой: в названии 6</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
+          <t>на странице другая книга: Lanpirot. Позывной «Хоттабыч»#7. Аватар "Х" (ч.2)</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; подтверждение правообладателя, к какой книге относится ссылка</t>
+          <t>серия и номер тома отдельными полями; подтверждение правообладателя, к какой книге относится ссылка</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Lilit Khachinyan</t>
+          <t>Lanpirot</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Guide de préparation à la production orale du DELF B2</t>
+          <t>Позывной «Хоттабыч»#9. Исчадие Кромки (ч. 2)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>https://languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2/</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 40% слов)</t>
-        </is>
-      </c>
+          <t>https://readtoday.ru/priklyucheniya/pozyvnoy-hottabych-9-ischadie-kromki-ch-2/</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Préparation à l’examen du DELF B2 – Language Learning</t>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>не нужны: страница удалена, ссылку можно закрыть</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Lost In Space</t>
+          <t>Larisa Lubimova</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Наследник, которого не должно быть</t>
+          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>https://mp3deer.cc/mp3/%D1%81%D1%83%D0%BF%D0%B5%D1%80-%D0%B0%D1%83%D0%B4%D0%B8%D0%BE%D0%BA%D0%BD%D0%B8%D0%B3%D0%B0-%D0%BD%D0%B0%D1%81%D0%BB%D0%B5%D0%B4%D0%BD%D0%B8%D0%BA-%D0%BA%D0%BE%D1%82%D0%BE%D1%80%D0%BE%D0%B3%D0%BE-%D0%BD%D0%B5-%D0%B4%D0%BE%D0%BB%D0%B6%D0%BD%D0%BE-%D0%B1%D1%8B%D1%82%D1%8C</t>
+          <t>https://librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
+          <t>адрес страницы не похож на название (совпало 39% слов)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr"/>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>на какие форматы есть права: текст, аудио</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Lucy Zen</t>
+          <t>Елена Полярная</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Автономия</t>
+          <t>Измена. Я вас верну</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>https://skladmk.online/product/energiya-zhizni-lucy-zen/</t>
+          <t>https://librain.ru/index.php/detektivy/izmena-ia-vas-vernu</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 200, Ошибка | Не удается получить доступ к сайту.</t>
-        </is>
-      </c>
+          <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; не нужны: страница удалена, ссылку можно закрыть</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="4" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Lilit Khachinyan</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Бракованный джинн</t>
+          <t>Guide de préparation à la production orale du DELF B2</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
+          <t>https://languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2/</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 40% слов)</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Préparation à l’examen du DELF B2 – Language Learning</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="4" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>MILA NENKA</t>
+          <t>Lost In Space</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
+          <t>Наследник, которого не должно быть</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>https://2ivdel.tvoysadik.ru/?section_id=98</t>
+          <t>https://mp3deer.cc/mp3/%D1%81%D1%83%D0%BF%D0%B5%D1%80-%D0%B0%D1%83%D0%B4%D0%B8%D0%BE%D0%BA%D0%BD%D0%B8%D0%B3%D0%B0-%D0%BD%D0%B0%D1%81%D0%BB%D0%B5%D0%B4%D0%BD%D0%B8%D0%BA-%D0%BA%D0%BE%D1%82%D0%BE%D1%80%D0%BE%D0%B3%D0%BE-%D0%BD%D0%B5-%D0%B4%D0%BE%D0%BB%D0%B6%D0%BD%D0%BE-%D0%B1%D1%8B%D1%82%D1%8C</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Занимательные раскраски</t>
-        </is>
-      </c>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; проверить, та ли ссылка указана для книги</t>
+          <t>на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="4" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Mind Wave</t>
+          <t>Lucy Zen</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Левитация. Путь к внутренней свободе</t>
+          <t>Автономия</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>https://mx-style.net/product/levitacziya-put-k-vnutrennej-svobode-mind-wave/</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Ошибка | Не удается получить доступ к сайту.</t>
-        </is>
-      </c>
+          <t>https://skladmk.online/product/energiya-zhizni-lucy-zen/</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Nika Nika</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Кето-рецепты</t>
+          <t>Бракованный джинн</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>https://librain.ru/zdorove/keto-recepty</t>
+          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr"/>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Кето-рецепты" совпало, но автора из каталога (Nika Nika) на странице нет. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -16451,263 +16391,267 @@
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Nina BROD</t>
+          <t>MILA NENKA</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Тишина</t>
+          <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>https://aknigi24.com/book/tisina-spokoistvie-v-mire-polnom-suma-tit-nat-xan-nikosho</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
+          <t>https://2ivdel.tvoysadik.ru/?section_id=98</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Тишина" совпало, но автора из каталога (Nina BROD) на странице нет. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Занимательные раскраски</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Findroid</t>
+          <t>Mind Wave</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Гнев Империи. Книга 1</t>
+          <t>Левитация. Путь к внутренней свободе</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr"/>
+          <t>https://mx-style.net/product/levitacziya-put-k-vnutrennej-svobode-mind-wave/</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Ошибка | Не удается получить доступ к сайту.</t>
+        </is>
+      </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>на какие форматы есть права: текст, аудио</t>
+          <t>не нужны: страница удалена, ссылку можно закрыть</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ominayashi</t>
+          <t>Nika Nika</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Пять звезд. Часть 5</t>
+          <t>Кето-рецепты</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>https://knigi.ebooker.online/book/42876144-kniga-pyat-zvezd.-chast-5</t>
+          <t>https://librain.ru/zdorove/keto-recepty</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Кето-рецепты" совпало, но автора из каталога (Nika Nika) на странице нет. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>не нужны: размещения нет</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="4" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Quartz Y</t>
+          <t>Nina BROD</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Переход в 5D измерение. Просветление. Методичка</t>
+          <t>Тишина</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>https://librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 25% слов)</t>
-        </is>
-      </c>
+          <t>https://aknigi24.com/book/tisina-spokoistvie-v-mire-polnom-suma-tit-nat-xan-nikosho</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полност</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Тишина" совпало, но автора из каталога (Nina BROD) на странице нет. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="4" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Rais Ais Gu</t>
+          <t>Findroid</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
+          <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>https://skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854/</t>
+          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="4" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Ominayashi</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Бракованный джинн</t>
+          <t>Пять звезд. Часть 5</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
+          <t>https://knigi.ebooker.online/book/42876144-kniga-pyat-zvezd.-chast-5</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>не нужны: размещения нет</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="4" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Quartz Y</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Констебль. Том III</t>
+          <t>Переход в 5D измерение. Просветление. Методичка</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+          <t>https://librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
+          <t>адрес страницы не похож на название (совпало 25% слов)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полностью fb2</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="4" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Rais Ais Gu</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Медовичок</t>
+          <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>https://litbox.pro/tag/ravenna/</t>
+          <t>https://skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854/</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Книги автора Равенна | LitBox | Равенна - скачать и читать все книги онлайн бесплатно полностью</t>
+          <t>на странице другая книга: Rais Ais Gu. Настроить свой мозг. Не можешь сосредоточиться? Забываешь всё на свете? Тянешь с решением?</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; подтверждение правообладателя, к какой книге относится ссылка</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="4" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
@@ -16716,18 +16660,18 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Медовичок</t>
+          <t>(Не)зачёт для птички</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>https://litseries.ru/romany/medovichok-533516/</t>
+          <t>https://litbox.pro/sovremennie-lyubovnie-romani/ne-zachyot-dlya-ptichki/</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 2): Название "(Не)зачёт для птички" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -16738,73 +16682,69 @@
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="4" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Галина Колоскова</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Измена. Хочу твоего мужа</t>
+          <t>Бракованный джинн</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>https://mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
-        </is>
-      </c>
+          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="4" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Медовичок</t>
+          <t>Констебль. Том III</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>https://pro-books.ru/liubovnye-romany/medovicok</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
+          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="4" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
@@ -16818,195 +16758,187 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>https://readtoday.ru/romany/medovichok-311872/</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
+          <t>https://litbox.pro/tag/ravenna/</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Книги автора Равенна | LitBox | Равенна - скачать и читать все книги онлайн бесплатно полностью</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="4" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Констебль. Том III</t>
+          <t>Медовичок</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr"/>
+          <t>https://litseries.ru/romany/medovichok-533516/</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="4" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Авее Лав</t>
+          <t>Галина Колоскова</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Ценадоверия</t>
+          <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>https://free-kniga.ru/romany/tsena-proscheniya-147884/</t>
+          <t>https://mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="4" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Авее Лав</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Ценадоверия</t>
+          <t>Медовичок</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>https://gigabooks.ru/romany/tsena-proscheniya-686299/</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
+          <t>https://pro-books.ru/liubovnye-romany/medovicok</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="4" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Авее Лав</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Ценадоверия</t>
+          <t>Медовичок</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>https://librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
+          <t>https://readtoday.ru/romany/medovichok-311872/</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="4" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Авее Лав</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Ценадоверия</t>
+          <t>Констебль. Том III</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>https://litseries.ru/romany/tsena-proscheniya-203253/</t>
+          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
-        </is>
-      </c>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="4" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
@@ -17020,24 +16952,28 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>https://free-kniga.ru/boevik/cena-doveriia/</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr"/>
+          <t>https://free-kniga.ru/romany/tsena-proscheniya-147884/</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. На странице указан автор: ИИ Текст. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="4" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
@@ -17051,7 +16987,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>https://wav-library.net/sovremennaia-proza/cena-proshheniia</t>
+          <t>https://gigabooks.ru/romany/tsena-proscheniya-686299/</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -17059,57 +16995,69 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="4" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Алекс Ключевской</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Тёмный маг. Книга 1. Неведомый путь</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>https://knigoline.ru/tyomnyy-mag-kniga-1-nevedomyy-put-4375/</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr"/>
+          <t>https://librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr"/>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="4" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Алекс Мара</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Разведенаипрекрасна</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>https://free-kniga.ru/yumor/razvedena-i-prekrasna-379393/</t>
+          <t>https://litseries.ru/romany/tsena-proscheniya-203253/</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -17117,140 +17065,140 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="4" t="n">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Алекс Коган</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>https://bibliophile.top/index.php?threads/11672/</t>
+          <t>https://free-kniga.ru/boevik/cena-doveriia/</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. На странице указан автор: ИИ Текст. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>не нужны: размещения нет</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="4" t="n">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Алекс Ключевской</t>
+          <t>Адриана Дари</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>13-й демон Асмодея. Том 2</t>
+          <t>Хозяйка Солнечного поместья</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>https://knigoline.ru/13-y-demon-asmodeya-tom-2-9093/</t>
+          <t>https://kniganet.ru/drama/nenuzhnaya-istinnaya-drakona-hozyayka-solnechnogo-pomestya/</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr"/>
+          <t>страница не подтвердила книгу (статус 2): Название "Хозяйка Солнечного поместья" совпало, но автора из каталога (Адриана Дари) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="4" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Алекс Коган</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>https://zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
+          <t>https://wav-library.net/sovremennaia-proza/cena-proshheniia</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 29% слов)</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
-        </is>
-      </c>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="4" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Алекс Крамер</t>
+          <t>Алекс Ключевской</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
+          <t>Тёмный маг. Книга 1. Неведомый путь</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>https://zoboko.com/book/rm9vg3d3/</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr"/>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
-        </is>
-      </c>
+          <t>https://knigoline.ru/tyomnyy-mag-kniga-1-nevedomyy-put-4375/</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="4" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
@@ -17264,7 +17212,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>https://readtoday.ru/yumor/razvedena-i-prekrasna-727057/</t>
+          <t>https://free-kniga.ru/yumor/razvedena-i-prekrasna-379393/</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -17281,270 +17229,704 @@
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="4" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Оксана Алексаева</t>
+          <t>Алекс Коган</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Измена. Я вас верну</t>
+          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>https://booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr"/>
+          <t>https://bibliophile.top/index.php?threads/11672/</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+          <t>не нужны: размещения нет</t>
         </is>
       </c>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="4" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Мария Авенская</t>
+          <t>Алекс Ключевской</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Измена. Хочу твоего мужа</t>
+          <t>13-й демон Асмодея. Том 2</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
-        </is>
-      </c>
+          <t>https://knigoline.ru/13-y-demon-asmodeya-tom-2-9093/</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
+          <t>страница не подтвердила книгу (статус 2): Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="4" t="n">
-        <v>138</v>
+        <v>112</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Арина Салай</t>
+          <t>Алекс Коган</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Измена. Я вас верну</t>
+          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>https://wav-library.net/proza/izmena-ia-vas-vernu</t>
+          <t>https://zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr"/>
+          <t>адрес страницы не похож на название (совпало 29% слов)</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
         </is>
       </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="4" t="n">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Дари Адриана</t>
+          <t>Алекс Крамер</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Хозяйка таверны "У Черных скал"</t>
+          <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>https://readtoday.ru/priklyucheniya/oklevetannaya-zhena-drakona-hozyayka-taverny-u-chernyh-skal-945787/</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
+          <t>https://zoboko.com/book/rm9vg3d3/</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="4" t="n">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Мария Авенская</t>
+          <t>Алекс Мара</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Измена. Хочу твоего мужа</t>
+          <t>Пухленькая Рыженькая</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
-        </is>
-      </c>
+          <t>https://libvi.ru/yumor/puhlenkaya-ryzhenkaya/</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Пухленькая Рыженькая" совпало, но автора из каталога (Алекс Мара) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="4" t="n">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Полина Рей</t>
+          <t>Алекс Мара</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Измена. Я вас верну</t>
+          <t>Разведенаипрекрасна</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>https://pro-books.ru/proza/izmena-ia-vas-vernu</t>
+          <t>https://readtoday.ru/yumor/razvedena-i-prekrasna-727057/</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
-        </is>
-      </c>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; подтверждение правообладателя, к какой книге относится ссылка</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="4" t="n">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Рудин Алекс</t>
+          <t>Алекс Найт</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Егерь-2: Назад в СССР</t>
+          <t>Девственность по контракту</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>https://free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853/</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>номер тома или части в адресе другой: в названии 2</t>
-        </is>
-      </c>
+          <t>https://kniganet.ru/fentezi/devstvennost-po-kontraktu/</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книг из каталога на странице нет. Страница про: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
+          <t>страница не подтвердила книгу (статус 2): Название "Девственность по контракту" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>серия и номер тома отдельными полями; проверить, та ли ссылка указана для книги</t>
+          <t>варианты имени автора и псевдонимы</t>
         </is>
       </c>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="4" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Егорова Надежда</t>
+          <t>Алекс Найт</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Ночь на Лысой горе. Где забытые боги слышат</t>
+          <t>Жена для Синей Бороды</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>https://lllit.ru/ezoterika/noc-na-lysoi-gore-gde-zabytye-bogi-slysat</t>
+          <t>https://kniganet.ru/romani/zhena-dlya-siney-borody/</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Жена для Синей Бороды" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="58" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>125</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Алекс Промтов</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Промтология. Большое руководство по нейросетям: от основ ИИ до готовых решений</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>https://s3.skladchinabiz.app/threads/promtologija-bolshoe-rukovodstvo-po-nejrosetjam-aleks-promtov.465616/</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="58" customHeight="1">
+      <c r="A56" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Оксана Алексаева</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>https://booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="58" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Мария Авенская</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="58" customHeight="1">
+      <c r="A58" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Алекс Рудин</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Тайновидец. Том 9: Повелитель стихий</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>https://kniganet.ru/priklyucheniya/taynovidets-tom-9-povelitel-stihiy/</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="58" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Алекс Рудин</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Тайновидец. Том 9: Повелитель стихий</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>https://libvi.ru/fentezi/taynovidets-tom-9-povelitel-stihiy/</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="58" customHeight="1">
+      <c r="A60" s="4" t="n">
+        <v>137</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Алекс Хот</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Двойное удовольствие</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>https://knigo-lub.ru/erotika/dvoynoe-udovolstvie/</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Двойное удовольствие" совпало, но автора из каталога (Алекс Хот) на странице нет. На странице указан автор: Mery. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="58" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Арина Салай</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>https://wav-library.net/proza/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="58" customHeight="1">
+      <c r="A62" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Дари Адриана</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Хозяйка таверны "У Черных скал"</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>https://readtoday.ru/priklyucheniya/oklevetannaya-zhena-drakona-hozyayka-taverny-u-chernyh-skal-945787/</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="58" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Мария Авенская</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="58" customHeight="1">
+      <c r="A64" s="4" t="n">
+        <v>143</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Мара Алекс</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Будь моим бывшим</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>https://litbox.pro/sovremennie-lyubovnie-romani/bud-moim-bivshim/</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 2): Название "Будь моим бывшим" совпало, но автора из каталога (Мара Алекс) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>варианты имени автора и псевдонимы</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="58" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Алекс Промтов</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Промтология. Большое руководство по нейросетям: от основ ИИ до готовых решений</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>https://skladchinabiz.app/threads/promtologija-bolshoe-rukovodstvo-po-nejrosetjam-aleks-promtov.465616/</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="58" customHeight="1">
+      <c r="A66" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Полина Рей</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>https://pro-books.ru/proza/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги; подтверждение правообладателя, к какой книге относится ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="58" customHeight="1">
+      <c r="A67" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Рудин Алекс</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Егерь-2: Назад в СССР</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>https://free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853/</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>номер тома или части в адресе другой: в названии 2</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>серия и номер тома отдельными полями; проверить, та ли ссылка указана для книги</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="58" customHeight="1">
+      <c r="A68" s="4" t="n">
+        <v>147</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Егорова Надежда</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Ночь на Лысой горе. Где забытые боги слышат</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>https://lllit.ru/ezoterika/noc-na-lysoi-gore-gde-zabytye-bogi-slysat</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
           <t>страница не подтвердила книгу (статус 0): Страницы нет: редирект на главную.</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>не нужны: страница удалена, ссылку можно закрыть</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17752,7 +18134,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>заголовок: Разреши любить. Позволь мне быть рядом. Книга 2 Анна Джейн; тип: application/pdf</t>
+          <t>заголовок: Разреши любить. Позволь мне быть рядом. Книга 2 Анна Джейн; автор на странице: Анна Джейн; тип: application/pdf</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -17762,7 +18144,7 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>Книг из каталога на странице нет. Страница про: Разреши любить. Позволь мне быть рядом. Книга 2 Анна Джейн</t>
+          <t>PDF найден и прочитан, но совпадение с каталогом не найдено. Обнаружено: Разреши любить. Позволь мне быть рядом. Книга 2 Анна Джейн</t>
         </is>
       </c>
     </row>
@@ -17815,7 +18197,7 @@
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>заголовок: Системный разведчик. Инфильтрация. Дилогия, Юрич Валерий - читать онлайн без регистрации</t>
+          <t>заголовок: Системный разведчик. Инфильтрация. Дилогия, Юрич Валерий - читать онлайн без регистрации; автор на странице: Юрич Валерий</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -18053,7 +18435,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -18067,17 +18449,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>заголовок: Ярость Вечных: скачать fb2, epub, pdf, txt | Антон Карелин; автор на странице: Антон Карелин; ИИ: решение уточнено, цитаты проверены</t>
+          <t>заголовок: Ярость Вечных: скачать fb2, epub, pdf, txt | Антон Карелин; автор на странице: Антон Карелин; ИИ: ИИ не дал проверяемого ответа, сохранено решение правил</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Антон Карелин. Ярость Вечных</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>ИИ-проверка: Есть совпадение названия и автора, но размещение книги не подтверждено: на сайте предлагается лишь покупка платной версии на партнёрском ресурсе.</t>
+          <t>Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18575,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>заголовок: Ясновидеть может каждый или как развить в себе сверхспособности, Хайр Хелен, книга полностью, читать бесплатно без сокращений</t>
+          <t>заголовок: Ясновидеть может каждый или как развить в себе сверхспособности, Хайр Хелен, книга полностью, читать бесплатно без сокращений; автор на странице: Хайр Хелен</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -18242,27 +18624,31 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>текст книги прямо на странице</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>200, нет содержимого</t>
+          <t>200, ok</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>заголовок: Загрузка — Библибоба</t>
+          <t>заголовок: Читать Я-Мир. Инструкция по переходу от внутренней гадости к истинной радости (Игорь Леонидович Науменко) бесплатно и полностью – книга жанра "Наука, ; автор на странице: Игорь Леонидович Науменко; загрузка: браузер Playwright</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>Игорь Леонидович Науменко. Я-Мир. Инструкция по переходу от внутренней гадости к истинной радости</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Сайт не отдал содержимое без браузера: проверка на бота или страница собирается скриптом.</t>
+          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: текст книги прямо на странице.</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18321,22 +18707,22 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>dolinakursov.ru/threads/disciplimit</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Проверить, что ссылка ведёт на эту книгу, а не на другой товар</t>
+          <t>URL содержит «sistema-kontrolja-reshenij», не совпадает с названием книги. Уточните привязку.</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Полный URL и подтверждение названия со страницы</t>
+          <t>подтверждение, что это тот же материал</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18346,22 +18732,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
+          <t>mp3deer.cc/mp3/armine-grigoryan</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Уточнить формат издания и соответствует ли ссылка ему</t>
+          <t>Ссылка ведёт на аудиоплеер, а тип записи - ebook. Также в slug армянское название.</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Полный URL, формат и обложка или описание страницы</t>
+          <t>ссылка на текст или смена типа на audio</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18371,22 +18757,22 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
+          <t>musportal.pro/track/1756600919</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Сверить формат с типом записи перед публикацией</t>
+          <t>URL страницы трека, а тип - ebook. Вероятно, ссылка на аудиокнигу.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Полный URL и явное указание формата</t>
+          <t>ссылка на текст или смена типа на audio</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
         </is>
       </c>
     </row>
@@ -18396,127 +18782,852 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+          <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Проверить автора и издание, не сливать книги разных авторов</t>
+          <t>Название дублируется у других авторов. Проверьте, не одно ли это произведение под разными именами.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ISBN или издательские данные для каждой версии</t>
+          <t>данные об авторстве или ISBN</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>dolinakursov.ru/threads/disciplimit</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Проверить соответствие ссылки названию и автору</t>
+          <t>Дублирует строку 2. Подтвердите, что это отдельная запись или уберите повтор.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Полный URL и название со страницы</t>
+          <t>решение о дубликате</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>в поле автора два написания, латиницей и кириллицей</t>
+          <t>astro-babylon.ru/biblioteca-main/</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Уточнить, это один автор или псевдоним, не склеивать записи</t>
+          <t>Slug «karmicheskaya-astrologiya» шире заголовка. Уточните, конкретна ли страница.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Ссылка на профиль автора и подтверждение написания</t>
+          <t>конкретная страница книги</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>номер тома или части в адресе другой: в названии 6</t>
+          <t>Jana Denole Яна Деноль</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Проверить номер тома в названии и на странице издания</t>
+          <t>В поле автора два написания. Выберите одно каноническое, другое перенесите в псевдонимы.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Полный URL и номер тома с обложки</t>
+          <t>каноническое написание имени</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>mp3deer.cc/mp3/armine-grigoryan</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Дублирует строку 7 с той же проблемой: ebook-тип при аудио-URL. Подтвердите или уберите.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>решение о дубликате и типе</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: qwen-3.8-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Проверить соответствие номера части в названии и в адресе страницы</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Точное название части и номер тома от правообладателя</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 39% слов)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Сверить ссылку и слишком длинное название, возможно это сборник</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Полный URL и структура названия из источника</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>ИИ: deepseek-v4.1-flash; цитата проверена</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Лайфхаки, фейлы и 100% полезной инфы</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Название не совпадает с адресом, возможно склеены две книги; уточнить одну книгу или серию</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Оригинальное название и ссылка со страницы книги</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Одно название у нескольких авторов; сверить автора и обложку с первоисточником</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Подтверждение авторства и ISBN или ID издания</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Guide de préparation à la production orale</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Адрес содержит пометку -2, возможен дубликат страницы; проверить каноническую ссылку</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Канонический URL и оригинальное название издания</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Наследник, которого не должно быть</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Тип ebook, а ссылка ведёт на аудио-раздел; уточнить формат издания</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Подтверждение формата и корректная ссылка на текст</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Автономия</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Адрес ведёт на другой товар того же автора; сверить название с карточкой товара</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Название по странице магазина и ID товара</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Мини-раскраска для самых маленьких</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Ссылка похожа на страницу раздела, а не книги; запросить прямую ссылку на издание</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Прямой URL карточки книги</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Гнев Империи. Книга 1</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Тип ebook, но ссылка на аудиотрек; проверить формат и источник</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Подтверждение формата и ссылка на ebook-издание</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>ИИ: glm-5.3-flash; цитата проверена</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Переход в 5D измерение. Просветление. Методичка</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 25% слов)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Констебль. Том III</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Медовичок</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: это же название есть у других авторов: Ася Исай, Мария Авенская</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Констебль. Том III</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Ценадоверия</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Разведенаипрекрасна</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 29% слов)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Разведенаипрекрасна</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Правила: ответ ИИ не подтверждён или API недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Хочу твоего мужа</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Измена. Я вас верну</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Егерь-2: Назад в СССР</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Проверить: номер тома или части в адресе другой: в названии 2</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>серия и номер тома отдельными полями</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Правила: превышено время ожидания ИИ</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E9"/>
+  <autoFilter ref="A1:E38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/out/result.xlsx
+++ b/out/result.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Задание 2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Строки'!$A$1:$S$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Строки'!$A$1:$P$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Книги'!$A$1:$I$92</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Дубли'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спорные'!$A$1:$G$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спорные'!$A$1:$F$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Задание 2'!$A$1:$M$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S151"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -459,9 +459,6 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="40" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="45" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,21 +542,6 @@
           <t>Спорно</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Проверка страницы: статус</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Проверка страницы: причина</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Книга на странице (ID)</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="n">
@@ -626,15 +608,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr"/>
     </row>
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="3" t="n">
@@ -701,15 +674,6 @@
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="3" t="n">
@@ -772,19 +736,6 @@
       </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>B5d524b</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -847,15 +798,6 @@
       </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -926,19 +868,6 @@
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>B1d85aa</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1005,15 +934,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Сайт ответил ошибкой 403, содержимое не получено.</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr"/>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -1076,15 +996,6 @@
       </c>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr"/>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -1147,15 +1058,6 @@
       </c>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr"/>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -1218,15 +1120,6 @@
       </c>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="n">
@@ -1293,19 +1186,6 @@
           <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание mp3; аудио, слушать онлайн.</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>B55d926</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1368,19 +1248,6 @@
       </c>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>B54dbaf</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1443,19 +1310,6 @@
       </c>
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>B54dbaf</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="n">
@@ -1522,15 +1376,6 @@
           <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>ИИ-проверка: Название совпадает, но указанный на странице автор Оксана Алексаева отсутствует среди кандидатов.</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr"/>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1593,19 +1438,6 @@
       </c>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>B54dbaf</t>
-        </is>
-      </c>
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -1668,19 +1500,6 @@
       </c>
       <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>B54dbaf</t>
-        </is>
-      </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1743,15 +1562,6 @@
       </c>
       <c r="O17" s="3" t="inlineStr"/>
       <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (Timeout).</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr"/>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="3" t="n">
@@ -1814,19 +1624,6 @@
       </c>
       <c r="O18" s="3" t="inlineStr"/>
       <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>B6e6b88</t>
-        </is>
-      </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1889,19 +1686,6 @@
       </c>
       <c r="O19" s="3" t="inlineStr"/>
       <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>B6e6b88</t>
-        </is>
-      </c>
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -1970,15 +1754,6 @@
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t>Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr"/>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -2041,19 +1816,6 @@
       </c>
       <c r="O21" s="3" t="inlineStr"/>
       <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t>B8d3aa4</t>
-        </is>
-      </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -2116,19 +1878,6 @@
       </c>
       <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>Ba91ddb</t>
-        </is>
-      </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -2191,19 +1940,6 @@
       </c>
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>Ba91ddb</t>
-        </is>
-      </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -2266,19 +2002,6 @@
       </c>
       <c r="O24" s="3" t="inlineStr"/>
       <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>B4abd1f</t>
-        </is>
-      </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -2341,19 +2064,6 @@
       </c>
       <c r="O25" s="3" t="inlineStr"/>
       <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>B5f8b85</t>
-        </is>
-      </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -2426,15 +2136,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr"/>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="3" t="n">
@@ -2497,19 +2198,6 @@
       </c>
       <c r="O27" s="3" t="inlineStr"/>
       <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t>ИИ-проверка: Название и автор (Хельга Дюран / Helga Duran) совпадают с каталогом, книга размещена с возможностью скачивания.</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t>B584abb</t>
-        </is>
-      </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -2572,19 +2260,6 @@
       </c>
       <c r="O28" s="3" t="inlineStr"/>
       <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>B584abb</t>
-        </is>
-      </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -2647,15 +2322,6 @@
       </c>
       <c r="O29" s="3" t="inlineStr"/>
       <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>Название "Тарский горячий твой" совпало, но автора из каталога (Helga Duran) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr"/>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -2718,19 +2384,6 @@
       </c>
       <c r="O30" s="3" t="inlineStr"/>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>B227ba1</t>
-        </is>
-      </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -2797,15 +2450,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Кармическая астрология | Книги по кармической астрологии</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="3" t="n">
@@ -2868,19 +2512,6 @@
       </c>
       <c r="O32" s="3" t="inlineStr"/>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>B38a21a</t>
-        </is>
-      </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -2947,19 +2578,6 @@
           <t>в поле автора два написания, латиницей и кириллицей</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: текст книги прямо на странице.</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>B754fe1</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="3" t="n">
@@ -3022,15 +2640,6 @@
       </c>
       <c r="O34" s="3" t="inlineStr"/>
       <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr"/>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -3103,15 +2712,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>Сайт ответил ошибкой 403, содержимое не получено.</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="3" t="n">
@@ -3174,19 +2774,6 @@
       </c>
       <c r="O36" s="3" t="inlineStr"/>
       <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: текст книги прямо на странице.</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>B571cdc</t>
-        </is>
-      </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="3" t="n">
@@ -3249,15 +2836,6 @@
       </c>
       <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr"/>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -3320,15 +2898,6 @@
       </c>
       <c r="O38" s="3" t="inlineStr"/>
       <c r="P38" s="3" t="inlineStr"/>
-      <c r="Q38" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
     </row>
     <row r="39" ht="58" customHeight="1">
       <c r="A39" s="3" t="n">
@@ -3391,19 +2960,6 @@
       </c>
       <c r="O39" s="3" t="inlineStr"/>
       <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>B9f7499</t>
-        </is>
-      </c>
     </row>
     <row r="40" ht="58" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -3466,19 +3022,6 @@
       </c>
       <c r="O40" s="3" t="inlineStr"/>
       <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t>B1f6137</t>
-        </is>
-      </c>
     </row>
     <row r="41" ht="58" customHeight="1">
       <c r="A41" s="3" t="n">
@@ -3541,19 +3084,6 @@
       </c>
       <c r="O41" s="3" t="inlineStr"/>
       <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>B644d34</t>
-        </is>
-      </c>
     </row>
     <row r="42" ht="58" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -3620,19 +3150,6 @@
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t>B27547e</t>
-        </is>
-      </c>
     </row>
     <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="n">
@@ -3699,19 +3216,6 @@
           <t>номер тома или части в адресе другой: в названии 6</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>B6ea970</t>
-        </is>
-      </c>
     </row>
     <row r="44" ht="58" customHeight="1">
       <c r="A44" s="3" t="n">
@@ -3774,19 +3278,6 @@
       </c>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>B6ea970</t>
-        </is>
-      </c>
     </row>
     <row r="45" ht="58" customHeight="1">
       <c r="A45" s="3" t="n">
@@ -3849,19 +3340,6 @@
       </c>
       <c r="O45" s="3" t="inlineStr"/>
       <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>B59d090</t>
-        </is>
-      </c>
     </row>
     <row r="46" ht="58" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -3924,15 +3402,6 @@
       </c>
       <c r="O46" s="3" t="inlineStr"/>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t>Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr"/>
     </row>
     <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="n">
@@ -3999,15 +3468,6 @@
           <t>адрес страницы не похож на название (совпало 39% слов)</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (Timeout).</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -4074,15 +3534,6 @@
           <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R48" s="2" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (Timeout).</t>
-        </is>
-      </c>
-      <c r="S48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="58" customHeight="1">
       <c r="A49" s="3" t="n">
@@ -4145,19 +3596,6 @@
       </c>
       <c r="O49" s="3" t="inlineStr"/>
       <c r="P49" s="3" t="inlineStr"/>
-      <c r="Q49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S49" s="3" t="inlineStr">
-        <is>
-          <t>B057496</t>
-        </is>
-      </c>
     </row>
     <row r="50" ht="58" customHeight="1">
       <c r="A50" s="3" t="n">
@@ -4222,15 +3660,6 @@
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr"/>
-      <c r="Q50" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R50" s="3" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (ConnectTimeout).</t>
-        </is>
-      </c>
-      <c r="S50" s="3" t="inlineStr"/>
     </row>
     <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="n">
@@ -4297,15 +3726,6 @@
           <t>адрес страницы не похож на название (совпало 40% слов)</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Préparation à l’examen du DELF B2 – Language Learning</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr"/>
     </row>
     <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -4372,15 +3792,6 @@
           <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Сайт ответил ошибкой 403, содержимое не получено.</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr"/>
     </row>
     <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="n">
@@ -4447,15 +3858,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>Получена страница ошибки вместо книги. Отсутствие книги не подтверждено, нужна повторная проверка.</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr"/>
     </row>
     <row r="54" ht="58" customHeight="1">
       <c r="A54" s="3" t="n">
@@ -4518,15 +3920,6 @@
       </c>
       <c r="O54" s="3" t="inlineStr"/>
       <c r="P54" s="3" t="inlineStr"/>
-      <c r="Q54" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R54" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S54" s="3" t="inlineStr"/>
     </row>
     <row r="55" ht="58" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -4589,19 +3982,6 @@
       </c>
       <c r="O55" s="3" t="inlineStr"/>
       <c r="P55" s="3" t="inlineStr"/>
-      <c r="Q55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S55" s="3" t="inlineStr">
-        <is>
-          <t>Bdaf254</t>
-        </is>
-      </c>
     </row>
     <row r="56" ht="58" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -4664,15 +4044,6 @@
       </c>
       <c r="O56" s="3" t="inlineStr"/>
       <c r="P56" s="3" t="inlineStr"/>
-      <c r="Q56" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R56" s="3" t="inlineStr">
-        <is>
-          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S56" s="3" t="inlineStr"/>
     </row>
     <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="n">
@@ -4739,15 +4110,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Занимательные раскраски</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="58" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -4810,15 +4172,6 @@
       </c>
       <c r="O58" s="3" t="inlineStr"/>
       <c r="P58" s="3" t="inlineStr"/>
-      <c r="Q58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="inlineStr">
-        <is>
-          <t>Страницы нет: ответ 404, Ошибка | Не удается получить доступ к сайту.</t>
-        </is>
-      </c>
-      <c r="S58" s="3" t="inlineStr"/>
     </row>
     <row r="59" ht="58" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -4881,19 +4234,6 @@
       </c>
       <c r="O59" s="3" t="inlineStr"/>
       <c r="P59" s="3" t="inlineStr"/>
-      <c r="Q59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S59" s="3" t="inlineStr">
-        <is>
-          <t>Be054eb</t>
-        </is>
-      </c>
     </row>
     <row r="60" ht="58" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -4956,15 +4296,6 @@
       </c>
       <c r="O60" s="3" t="inlineStr"/>
       <c r="P60" s="3" t="inlineStr"/>
-      <c r="Q60" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R60" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S60" s="3" t="inlineStr"/>
     </row>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -5027,15 +4358,6 @@
       </c>
       <c r="O61" s="3" t="inlineStr"/>
       <c r="P61" s="3" t="inlineStr"/>
-      <c r="Q61" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R61" s="3" t="inlineStr">
-        <is>
-          <t>Название "Кето-рецепты" совпало, но автора из каталога (Nika Nika) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S61" s="3" t="inlineStr"/>
     </row>
     <row r="62" ht="58" customHeight="1">
       <c r="A62" s="3" t="n">
@@ -5098,15 +4420,6 @@
       </c>
       <c r="O62" s="3" t="inlineStr"/>
       <c r="P62" s="3" t="inlineStr"/>
-      <c r="Q62" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R62" s="3" t="inlineStr">
-        <is>
-          <t>Название "Тишина" совпало, но автора из каталога (Nina BROD) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S62" s="3" t="inlineStr"/>
     </row>
     <row r="63" ht="58" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -5169,19 +4482,6 @@
       </c>
       <c r="O63" s="3" t="inlineStr"/>
       <c r="P63" s="3" t="inlineStr"/>
-      <c r="Q63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S63" s="3" t="inlineStr">
-        <is>
-          <t>B7ff39c</t>
-        </is>
-      </c>
     </row>
     <row r="64" ht="58" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -5254,19 +4554,6 @@
           <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="Q64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание mp3; аудио, слушать онлайн.</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>B55d926</t>
-        </is>
-      </c>
     </row>
     <row r="65" ht="58" customHeight="1">
       <c r="A65" s="3" t="n">
@@ -5329,19 +4616,6 @@
       </c>
       <c r="O65" s="3" t="inlineStr"/>
       <c r="P65" s="3" t="inlineStr"/>
-      <c r="Q65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
-        </is>
-      </c>
-      <c r="S65" s="3" t="inlineStr">
-        <is>
-          <t>B2c0d9e</t>
-        </is>
-      </c>
     </row>
     <row r="66" ht="58" customHeight="1">
       <c r="A66" s="3" t="n">
@@ -5404,19 +4678,6 @@
       </c>
       <c r="O66" s="3" t="inlineStr"/>
       <c r="P66" s="3" t="inlineStr"/>
-      <c r="Q66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R66" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: текст книги прямо на странице.</t>
-        </is>
-      </c>
-      <c r="S66" s="3" t="inlineStr">
-        <is>
-          <t>B2c0d9e</t>
-        </is>
-      </c>
     </row>
     <row r="67" ht="58" customHeight="1">
       <c r="A67" s="2" t="n">
@@ -5483,15 +4744,6 @@
           <t>адрес страницы не похож на название (совпало 25% слов)</t>
         </is>
       </c>
-      <c r="Q67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полностью fb2</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="58" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -5558,19 +4810,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="inlineStr">
-        <is>
-          <t>B4b3214</t>
-        </is>
-      </c>
     </row>
     <row r="69" ht="58" customHeight="1">
       <c r="A69" s="3" t="n">
@@ -5633,15 +4872,6 @@
       </c>
       <c r="O69" s="3" t="inlineStr"/>
       <c r="P69" s="3" t="inlineStr"/>
-      <c r="Q69" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S69" s="3" t="inlineStr"/>
     </row>
     <row r="70" ht="58" customHeight="1">
       <c r="A70" s="3" t="n">
@@ -5710,19 +4940,6 @@
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr"/>
-      <c r="Q70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S70" s="3" t="inlineStr">
-        <is>
-          <t>Bdaf254</t>
-        </is>
-      </c>
     </row>
     <row r="71" ht="58" customHeight="1">
       <c r="A71" s="3" t="n">
@@ -5785,19 +5002,6 @@
       </c>
       <c r="O71" s="3" t="inlineStr"/>
       <c r="P71" s="3" t="inlineStr"/>
-      <c r="Q71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R71" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S71" s="3" t="inlineStr">
-        <is>
-          <t>B4b3214</t>
-        </is>
-      </c>
     </row>
     <row r="72" ht="58" customHeight="1">
       <c r="A72" s="3" t="n">
@@ -5860,15 +5064,6 @@
       </c>
       <c r="O72" s="3" t="inlineStr"/>
       <c r="P72" s="3" t="inlineStr"/>
-      <c r="Q72" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R72" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S72" s="3" t="inlineStr"/>
     </row>
     <row r="73" ht="58" customHeight="1">
       <c r="A73" s="3" t="n">
@@ -5931,15 +5126,6 @@
       </c>
       <c r="O73" s="3" t="inlineStr"/>
       <c r="P73" s="3" t="inlineStr"/>
-      <c r="Q73" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R73" s="3" t="inlineStr">
-        <is>
-          <t>Название "(Не)зачёт для птички" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S73" s="3" t="inlineStr"/>
     </row>
     <row r="74" ht="58" customHeight="1">
       <c r="A74" s="3" t="n">
@@ -6008,15 +5194,6 @@
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr"/>
-      <c r="Q74" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R74" s="3" t="inlineStr">
-        <is>
-          <t>Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S74" s="3" t="inlineStr"/>
     </row>
     <row r="75" ht="58" customHeight="1">
       <c r="A75" s="2" t="n">
@@ -6083,19 +5260,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R75" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в тексте страницы (сборник или список), автор совпал. Признаки размещения: скачивание mp3, zip; файлообменники htfl.net, nitroflare.com, trbt.cc; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S75" s="2" t="inlineStr">
-        <is>
-          <t>B10fce6</t>
-        </is>
-      </c>
     </row>
     <row r="76" ht="58" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -6162,15 +5326,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Книги автора Равенна | LitBox | Равенна - скачать и читать все книги онлайн бесплатно полностью</t>
-        </is>
-      </c>
-      <c r="S76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="58" customHeight="1">
       <c r="A77" s="3" t="n">
@@ -6233,15 +5388,6 @@
       </c>
       <c r="O77" s="3" t="inlineStr"/>
       <c r="P77" s="3" t="inlineStr"/>
-      <c r="Q77" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R77" s="3" t="inlineStr">
-        <is>
-          <t>Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S77" s="3" t="inlineStr"/>
     </row>
     <row r="78" ht="58" customHeight="1">
       <c r="A78" s="2" t="n">
@@ -6308,15 +5454,6 @@
           <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
         </is>
       </c>
-      <c r="Q78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="58" customHeight="1">
       <c r="A79" s="3" t="n">
@@ -6379,15 +5516,6 @@
       </c>
       <c r="O79" s="3" t="inlineStr"/>
       <c r="P79" s="3" t="inlineStr"/>
-      <c r="Q79" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R79" s="3" t="inlineStr">
-        <is>
-          <t>Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S79" s="3" t="inlineStr"/>
     </row>
     <row r="80" ht="58" customHeight="1">
       <c r="A80" s="3" t="n">
@@ -6450,15 +5578,6 @@
       </c>
       <c r="O80" s="3" t="inlineStr"/>
       <c r="P80" s="3" t="inlineStr"/>
-      <c r="Q80" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R80" s="3" t="inlineStr">
-        <is>
-          <t>Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S80" s="3" t="inlineStr"/>
     </row>
     <row r="81" ht="58" customHeight="1">
       <c r="A81" s="3" t="n">
@@ -6521,19 +5640,6 @@
       </c>
       <c r="O81" s="3" t="inlineStr"/>
       <c r="P81" s="3" t="inlineStr"/>
-      <c r="Q81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R81" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S81" s="3" t="inlineStr">
-        <is>
-          <t>B8b83ea</t>
-        </is>
-      </c>
     </row>
     <row r="82" ht="58" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -6606,19 +5712,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R82" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в тексте страницы (сборник или список), автор совпал. Признаки размещения: скачивание mp3, zip; файлообменники htfl.net, nitroflare.com, trbt.cc; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S82" s="2" t="inlineStr">
-        <is>
-          <t>B10fce6</t>
-        </is>
-      </c>
     </row>
     <row r="83" ht="58" customHeight="1">
       <c r="A83" s="3" t="n">
@@ -6685,15 +5778,6 @@
         </is>
       </c>
       <c r="P83" s="3" t="inlineStr"/>
-      <c r="Q83" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R83" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S83" s="3" t="inlineStr"/>
     </row>
     <row r="84" ht="58" customHeight="1">
       <c r="A84" s="3" t="n">
@@ -6762,19 +5846,6 @@
         </is>
       </c>
       <c r="P84" s="3" t="inlineStr"/>
-      <c r="Q84" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R84" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S84" s="3" t="inlineStr">
-        <is>
-          <t>B8b83ea</t>
-        </is>
-      </c>
     </row>
     <row r="85" ht="58" customHeight="1">
       <c r="A85" s="3" t="n">
@@ -6837,19 +5908,6 @@
       </c>
       <c r="O85" s="3" t="inlineStr"/>
       <c r="P85" s="3" t="inlineStr"/>
-      <c r="Q85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R85" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S85" s="3" t="inlineStr">
-        <is>
-          <t>B8b7f62</t>
-        </is>
-      </c>
     </row>
     <row r="86" ht="58" customHeight="1">
       <c r="A86" s="3" t="n">
@@ -6912,15 +5970,6 @@
       </c>
       <c r="O86" s="3" t="inlineStr"/>
       <c r="P86" s="3" t="inlineStr"/>
-      <c r="Q86" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R86" s="3" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (ConnectionError).</t>
-        </is>
-      </c>
-      <c r="S86" s="3" t="inlineStr"/>
     </row>
     <row r="87" ht="58" customHeight="1">
       <c r="A87" s="2" t="n">
@@ -6987,15 +6036,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
-        </is>
-      </c>
-      <c r="S87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="58" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -7062,15 +6102,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
-        </is>
-      </c>
-      <c r="S88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="58" customHeight="1">
       <c r="A89" s="2" t="n">
@@ -7137,15 +6168,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
-        </is>
-      </c>
-      <c r="S89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="58" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -7212,15 +6234,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
-        </is>
-      </c>
-      <c r="S90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="58" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -7283,19 +6296,6 @@
       </c>
       <c r="O91" s="3" t="inlineStr"/>
       <c r="P91" s="3" t="inlineStr"/>
-      <c r="Q91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R91" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S91" s="3" t="inlineStr">
-        <is>
-          <t>B6715b7</t>
-        </is>
-      </c>
     </row>
     <row r="92" ht="58" customHeight="1">
       <c r="A92" s="3" t="n">
@@ -7364,19 +6364,6 @@
         </is>
       </c>
       <c r="P92" s="3" t="inlineStr"/>
-      <c r="Q92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S92" s="3" t="inlineStr">
-        <is>
-          <t>B8b7f62</t>
-        </is>
-      </c>
     </row>
     <row r="93" ht="58" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -7439,15 +6426,6 @@
       </c>
       <c r="O93" s="3" t="inlineStr"/>
       <c r="P93" s="3" t="inlineStr"/>
-      <c r="Q93" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R93" s="3" t="inlineStr">
-        <is>
-          <t>Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. На странице указан автор: ИИ Текст. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S93" s="3" t="inlineStr"/>
     </row>
     <row r="94" ht="58" customHeight="1">
       <c r="A94" s="3" t="n">
@@ -7510,19 +6488,6 @@
       </c>
       <c r="O94" s="3" t="inlineStr"/>
       <c r="P94" s="3" t="inlineStr"/>
-      <c r="Q94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R94" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S94" s="3" t="inlineStr">
-        <is>
-          <t>B14dce4</t>
-        </is>
-      </c>
     </row>
     <row r="95" ht="58" customHeight="1">
       <c r="A95" s="3" t="n">
@@ -7591,19 +6556,6 @@
         </is>
       </c>
       <c r="P95" s="3" t="inlineStr"/>
-      <c r="Q95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R95" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S95" s="3" t="inlineStr">
-        <is>
-          <t>B14dce4</t>
-        </is>
-      </c>
     </row>
     <row r="96" ht="58" customHeight="1">
       <c r="A96" s="3" t="n">
@@ -7670,15 +6622,6 @@
         </is>
       </c>
       <c r="P96" s="3" t="inlineStr"/>
-      <c r="Q96" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R96" s="3" t="inlineStr">
-        <is>
-          <t>Название "Хозяйка Солнечного поместья" совпало, но автора из каталога (Адриана Дари) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S96" s="3" t="inlineStr"/>
     </row>
     <row r="97" ht="58" customHeight="1">
       <c r="A97" s="3" t="n">
@@ -7741,15 +6684,6 @@
       </c>
       <c r="O97" s="3" t="inlineStr"/>
       <c r="P97" s="3" t="inlineStr"/>
-      <c r="Q97" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R97" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S97" s="3" t="inlineStr"/>
     </row>
     <row r="98" ht="58" customHeight="1">
       <c r="A98" s="3" t="n">
@@ -7818,15 +6752,6 @@
         </is>
       </c>
       <c r="P98" s="3" t="inlineStr"/>
-      <c r="Q98" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R98" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S98" s="3" t="inlineStr"/>
     </row>
     <row r="99" ht="58" customHeight="1">
       <c r="A99" s="2" t="n">
@@ -7893,15 +6818,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R99" s="2" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (SSLError).</t>
-        </is>
-      </c>
-      <c r="S99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="58" customHeight="1">
       <c r="A100" s="3" t="n">
@@ -7970,15 +6886,6 @@
         </is>
       </c>
       <c r="P100" s="3" t="inlineStr"/>
-      <c r="Q100" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R100" s="3" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (ConnectionError).</t>
-        </is>
-      </c>
-      <c r="S100" s="3" t="inlineStr"/>
     </row>
     <row r="101" ht="58" customHeight="1">
       <c r="A101" s="3" t="n">
@@ -8041,19 +6948,6 @@
       </c>
       <c r="O101" s="3" t="inlineStr"/>
       <c r="P101" s="3" t="inlineStr"/>
-      <c r="Q101" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
-        </is>
-      </c>
-      <c r="S101" s="3" t="inlineStr">
-        <is>
-          <t>Be729d7</t>
-        </is>
-      </c>
     </row>
     <row r="102" ht="58" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -8124,19 +7018,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R102" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S102" s="2" t="inlineStr">
-        <is>
-          <t>B92dcc8</t>
-        </is>
-      </c>
     </row>
     <row r="103" ht="58" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -8199,15 +7080,6 @@
       </c>
       <c r="O103" s="3" t="inlineStr"/>
       <c r="P103" s="3" t="inlineStr"/>
-      <c r="Q103" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R103" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S103" s="3" t="inlineStr"/>
     </row>
     <row r="104" ht="58" customHeight="1">
       <c r="A104" s="3" t="n">
@@ -8276,19 +7148,6 @@
         </is>
       </c>
       <c r="P104" s="3" t="inlineStr"/>
-      <c r="Q104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R104" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание fb2; чтение онлайн.</t>
-        </is>
-      </c>
-      <c r="S104" s="3" t="inlineStr">
-        <is>
-          <t>B6715b7</t>
-        </is>
-      </c>
     </row>
     <row r="105" ht="58" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -8351,19 +7210,6 @@
       </c>
       <c r="O105" s="3" t="inlineStr"/>
       <c r="P105" s="3" t="inlineStr"/>
-      <c r="Q105" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R105" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S105" s="3" t="inlineStr">
-        <is>
-          <t>Ba6e475</t>
-        </is>
-      </c>
     </row>
     <row r="106" ht="58" customHeight="1">
       <c r="A106" s="3" t="n">
@@ -8426,19 +7272,6 @@
       </c>
       <c r="O106" s="3" t="inlineStr"/>
       <c r="P106" s="3" t="inlineStr"/>
-      <c r="Q106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R106" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S106" s="3" t="inlineStr">
-        <is>
-          <t>Ba6e475</t>
-        </is>
-      </c>
     </row>
     <row r="107" ht="58" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -8503,19 +7336,6 @@
         </is>
       </c>
       <c r="P107" s="3" t="inlineStr"/>
-      <c r="Q107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
-        </is>
-      </c>
-      <c r="S107" s="3" t="inlineStr">
-        <is>
-          <t>Bbec4dd</t>
-        </is>
-      </c>
     </row>
     <row r="108" ht="58" customHeight="1">
       <c r="A108" s="3" t="n">
@@ -8580,15 +7400,6 @@
         </is>
       </c>
       <c r="P108" s="3" t="inlineStr"/>
-      <c r="Q108" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R108" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S108" s="3" t="inlineStr"/>
     </row>
     <row r="109" ht="58" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -8659,19 +7470,6 @@
         </is>
       </c>
       <c r="P109" s="3" t="inlineStr"/>
-      <c r="Q109" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R109" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
-        </is>
-      </c>
-      <c r="S109" s="3" t="inlineStr">
-        <is>
-          <t>B9fc9a4</t>
-        </is>
-      </c>
     </row>
     <row r="110" ht="58" customHeight="1">
       <c r="A110" s="3" t="n">
@@ -8734,19 +7532,6 @@
       </c>
       <c r="O110" s="3" t="inlineStr"/>
       <c r="P110" s="3" t="inlineStr"/>
-      <c r="Q110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R110" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S110" s="3" t="inlineStr">
-        <is>
-          <t>Bbec4dd</t>
-        </is>
-      </c>
     </row>
     <row r="111" ht="58" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -8809,15 +7594,6 @@
       </c>
       <c r="O111" s="3" t="inlineStr"/>
       <c r="P111" s="3" t="inlineStr"/>
-      <c r="Q111" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R111" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S111" s="3" t="inlineStr"/>
     </row>
     <row r="112" ht="58" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -8884,15 +7660,6 @@
           <t>адрес страницы не похож на название (совпало 29% слов)</t>
         </is>
       </c>
-      <c r="Q112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
-        </is>
-      </c>
-      <c r="S112" s="2" t="inlineStr"/>
     </row>
     <row r="113" ht="58" customHeight="1">
       <c r="A113" s="3" t="n">
@@ -8955,19 +7722,6 @@
       </c>
       <c r="O113" s="3" t="inlineStr"/>
       <c r="P113" s="3" t="inlineStr"/>
-      <c r="Q113" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R113" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S113" s="3" t="inlineStr">
-        <is>
-          <t>B3e38f6</t>
-        </is>
-      </c>
     </row>
     <row r="114" ht="58" customHeight="1">
       <c r="A114" s="3" t="n">
@@ -9030,19 +7784,6 @@
       </c>
       <c r="O114" s="3" t="inlineStr"/>
       <c r="P114" s="3" t="inlineStr"/>
-      <c r="Q114" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R114" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S114" s="3" t="inlineStr">
-        <is>
-          <t>Bd7dc3e</t>
-        </is>
-      </c>
     </row>
     <row r="115" ht="58" customHeight="1">
       <c r="A115" s="3" t="n">
@@ -9105,19 +7846,6 @@
       </c>
       <c r="O115" s="3" t="inlineStr"/>
       <c r="P115" s="3" t="inlineStr"/>
-      <c r="Q115" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S115" s="3" t="inlineStr">
-        <is>
-          <t>Be7cb4c</t>
-        </is>
-      </c>
     </row>
     <row r="116" ht="58" customHeight="1">
       <c r="A116" s="3" t="n">
@@ -9180,15 +7908,6 @@
       </c>
       <c r="O116" s="3" t="inlineStr"/>
       <c r="P116" s="3" t="inlineStr"/>
-      <c r="Q116" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R116" s="3" t="inlineStr">
-        <is>
-          <t>Сайт ответил ошибкой 513, содержимое не получено.</t>
-        </is>
-      </c>
-      <c r="S116" s="3" t="inlineStr"/>
     </row>
     <row r="117" ht="58" customHeight="1">
       <c r="A117" s="2" t="n">
@@ -9255,19 +7974,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q117" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R117" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S117" s="2" t="inlineStr">
-        <is>
-          <t>Bd7dc3e</t>
-        </is>
-      </c>
     </row>
     <row r="118" ht="58" customHeight="1">
       <c r="A118" s="3" t="n">
@@ -9334,15 +8040,6 @@
         </is>
       </c>
       <c r="P118" s="3" t="inlineStr"/>
-      <c r="Q118" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R118" s="3" t="inlineStr">
-        <is>
-          <t>Название "Пухленькая Рыженькая" совпало, но автора из каталога (Алекс Мара) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S118" s="3" t="inlineStr"/>
     </row>
     <row r="119" ht="58" customHeight="1">
       <c r="A119" s="2" t="n">
@@ -9413,19 +8110,6 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="Q119" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R119" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S119" s="2" t="inlineStr">
-        <is>
-          <t>B92dcc8</t>
-        </is>
-      </c>
     </row>
     <row r="120" ht="58" customHeight="1">
       <c r="A120" s="3" t="n">
@@ -9488,15 +8172,6 @@
       </c>
       <c r="O120" s="3" t="inlineStr"/>
       <c r="P120" s="3" t="inlineStr"/>
-      <c r="Q120" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R120" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S120" s="3" t="inlineStr"/>
     </row>
     <row r="121" ht="58" customHeight="1">
       <c r="A121" s="3" t="n">
@@ -9559,15 +8234,6 @@
       </c>
       <c r="O121" s="3" t="inlineStr"/>
       <c r="P121" s="3" t="inlineStr"/>
-      <c r="Q121" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R121" s="3" t="inlineStr">
-        <is>
-          <t>Название "Девственность по контракту" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S121" s="3" t="inlineStr"/>
     </row>
     <row r="122" ht="58" customHeight="1">
       <c r="A122" s="3" t="n">
@@ -9630,15 +8296,6 @@
       </c>
       <c r="O122" s="3" t="inlineStr"/>
       <c r="P122" s="3" t="inlineStr"/>
-      <c r="Q122" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R122" s="3" t="inlineStr">
-        <is>
-          <t>Сайт ответил ошибкой 500, содержимое не получено.</t>
-        </is>
-      </c>
-      <c r="S122" s="3" t="inlineStr"/>
     </row>
     <row r="123" ht="58" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -9701,15 +8358,6 @@
       </c>
       <c r="O123" s="3" t="inlineStr"/>
       <c r="P123" s="3" t="inlineStr"/>
-      <c r="Q123" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R123" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S123" s="3" t="inlineStr"/>
     </row>
     <row r="124" ht="58" customHeight="1">
       <c r="A124" s="3" t="n">
@@ -9772,15 +8420,6 @@
       </c>
       <c r="O124" s="3" t="inlineStr"/>
       <c r="P124" s="3" t="inlineStr"/>
-      <c r="Q124" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R124" s="3" t="inlineStr">
-        <is>
-          <t>Название "Жена для Синей Бороды" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S124" s="3" t="inlineStr"/>
     </row>
     <row r="125" ht="58" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -9843,15 +8482,6 @@
       </c>
       <c r="O125" s="3" t="inlineStr"/>
       <c r="P125" s="3" t="inlineStr"/>
-      <c r="Q125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" s="3" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
-        </is>
-      </c>
-      <c r="S125" s="3" t="inlineStr"/>
     </row>
     <row r="126" ht="58" customHeight="1">
       <c r="A126" s="2" t="n">
@@ -9918,19 +8548,6 @@
           <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
         </is>
       </c>
-      <c r="Q126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R126" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S126" s="2" t="inlineStr">
-        <is>
-          <t>B0930d2</t>
-        </is>
-      </c>
     </row>
     <row r="127" ht="58" customHeight="1">
       <c r="A127" s="2" t="n">
@@ -9997,15 +8614,6 @@
           <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
         </is>
       </c>
-      <c r="Q127" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R127" s="2" t="inlineStr">
-        <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S127" s="2" t="inlineStr"/>
     </row>
     <row r="128" ht="58" customHeight="1">
       <c r="A128" s="3" t="n">
@@ -10074,15 +8682,6 @@
         </is>
       </c>
       <c r="P128" s="3" t="inlineStr"/>
-      <c r="Q128" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R128" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S128" s="3" t="inlineStr"/>
     </row>
     <row r="129" ht="58" customHeight="1">
       <c r="A129" s="3" t="n">
@@ -10149,19 +8748,6 @@
         </is>
       </c>
       <c r="P129" s="3" t="inlineStr"/>
-      <c r="Q129" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R129" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S129" s="3" t="inlineStr">
-        <is>
-          <t>B0e3c4d</t>
-        </is>
-      </c>
     </row>
     <row r="130" ht="58" customHeight="1">
       <c r="A130" s="3" t="n">
@@ -10228,19 +8814,6 @@
         </is>
       </c>
       <c r="P130" s="3" t="inlineStr"/>
-      <c r="Q130" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R130" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S130" s="3" t="inlineStr">
-        <is>
-          <t>Bce9a30</t>
-        </is>
-      </c>
     </row>
     <row r="131" ht="58" customHeight="1">
       <c r="A131" s="3" t="n">
@@ -10307,15 +8880,6 @@
         </is>
       </c>
       <c r="P131" s="3" t="inlineStr"/>
-      <c r="Q131" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R131" s="3" t="inlineStr">
-        <is>
-          <t>Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S131" s="3" t="inlineStr"/>
     </row>
     <row r="132" ht="58" customHeight="1">
       <c r="A132" s="3" t="n">
@@ -10382,19 +8946,6 @@
         </is>
       </c>
       <c r="P132" s="3" t="inlineStr"/>
-      <c r="Q132" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R132" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S132" s="3" t="inlineStr">
-        <is>
-          <t>Bce9a30</t>
-        </is>
-      </c>
     </row>
     <row r="133" ht="58" customHeight="1">
       <c r="A133" s="3" t="n">
@@ -10461,15 +9012,6 @@
         </is>
       </c>
       <c r="P133" s="3" t="inlineStr"/>
-      <c r="Q133" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R133" s="3" t="inlineStr">
-        <is>
-          <t>Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S133" s="3" t="inlineStr"/>
     </row>
     <row r="134" ht="58" customHeight="1">
       <c r="A134" s="3" t="n">
@@ -10536,19 +9078,6 @@
         </is>
       </c>
       <c r="P134" s="3" t="inlineStr"/>
-      <c r="Q134" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R134" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S134" s="3" t="inlineStr">
-        <is>
-          <t>Bce9a30</t>
-        </is>
-      </c>
     </row>
     <row r="135" ht="58" customHeight="1">
       <c r="A135" s="3" t="n">
@@ -10615,19 +9144,6 @@
         </is>
       </c>
       <c r="P135" s="3" t="inlineStr"/>
-      <c r="Q135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R135" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S135" s="3" t="inlineStr">
-        <is>
-          <t>Bce9a30</t>
-        </is>
-      </c>
     </row>
     <row r="136" ht="58" customHeight="1">
       <c r="A136" s="3" t="n">
@@ -10694,19 +9210,6 @@
         </is>
       </c>
       <c r="P136" s="3" t="inlineStr"/>
-      <c r="Q136" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R136" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S136" s="3" t="inlineStr">
-        <is>
-          <t>Bce9a30</t>
-        </is>
-      </c>
     </row>
     <row r="137" ht="58" customHeight="1">
       <c r="A137" s="3" t="n">
@@ -10769,15 +9272,6 @@
       </c>
       <c r="O137" s="3" t="inlineStr"/>
       <c r="P137" s="3" t="inlineStr"/>
-      <c r="Q137" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R137" s="3" t="inlineStr">
-        <is>
-          <t>Название "Двойное удовольствие" совпало, но автора из каталога (Алекс Хот) на странице нет. На странице указан автор: Mery. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S137" s="3" t="inlineStr"/>
     </row>
     <row r="138" ht="58" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -10844,15 +9338,6 @@
           <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
         </is>
       </c>
-      <c r="Q138" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R138" s="2" t="inlineStr">
-        <is>
-          <t>Сайт не ответил (SSLError).</t>
-        </is>
-      </c>
-      <c r="S138" s="2" t="inlineStr"/>
     </row>
     <row r="139" ht="58" customHeight="1">
       <c r="A139" s="3" t="n">
@@ -10919,15 +9404,6 @@
         </is>
       </c>
       <c r="P139" s="3" t="inlineStr"/>
-      <c r="Q139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" s="3" t="inlineStr">
-        <is>
-          <t>Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
-      <c r="S139" s="3" t="inlineStr"/>
     </row>
     <row r="140" ht="58" customHeight="1">
       <c r="A140" s="3" t="n">
@@ -10990,15 +9466,6 @@
       </c>
       <c r="O140" s="3" t="inlineStr"/>
       <c r="P140" s="3" t="inlineStr"/>
-      <c r="Q140" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R140" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S140" s="3" t="inlineStr"/>
     </row>
     <row r="141" ht="58" customHeight="1">
       <c r="A141" s="3" t="n">
@@ -11067,19 +9534,6 @@
         </is>
       </c>
       <c r="P141" s="3" t="inlineStr"/>
-      <c r="Q141" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R141" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S141" s="3" t="inlineStr">
-        <is>
-          <t>Be7cb4c</t>
-        </is>
-      </c>
     </row>
     <row r="142" ht="58" customHeight="1">
       <c r="A142" s="2" t="n">
@@ -11152,15 +9606,6 @@
           <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
         </is>
       </c>
-      <c r="Q142" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="R142" s="2" t="inlineStr">
-        <is>
-          <t>Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S142" s="2" t="inlineStr"/>
     </row>
     <row r="143" ht="58" customHeight="1">
       <c r="A143" s="3" t="n">
@@ -11227,15 +9672,6 @@
         </is>
       </c>
       <c r="P143" s="3" t="inlineStr"/>
-      <c r="Q143" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R143" s="3" t="inlineStr">
-        <is>
-          <t>Название "Будь моим бывшим" совпало, но автора из каталога (Мара Алекс) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="S143" s="3" t="inlineStr"/>
     </row>
     <row r="144" ht="58" customHeight="1">
       <c r="A144" s="3" t="n">
@@ -11304,15 +9740,6 @@
         </is>
       </c>
       <c r="P144" s="3" t="inlineStr"/>
-      <c r="Q144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R144" s="3" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
-        </is>
-      </c>
-      <c r="S144" s="3" t="inlineStr"/>
     </row>
     <row r="145" ht="58" customHeight="1">
       <c r="A145" s="2" t="n">
@@ -11379,19 +9806,6 @@
           <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
         </is>
       </c>
-      <c r="Q145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R145" s="2" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S145" s="2" t="inlineStr">
-        <is>
-          <t>B0930d2</t>
-        </is>
-      </c>
     </row>
     <row r="146" ht="58" customHeight="1">
       <c r="A146" s="2" t="n">
@@ -11462,15 +9876,6 @@
           <t>номер тома или части в адресе другой: в названии 2</t>
         </is>
       </c>
-      <c r="Q146" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" s="2" t="inlineStr">
-        <is>
-          <t>Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
-        </is>
-      </c>
-      <c r="S146" s="2" t="inlineStr"/>
     </row>
     <row r="147" ht="58" customHeight="1">
       <c r="A147" s="3" t="n">
@@ -11541,15 +9946,6 @@
         </is>
       </c>
       <c r="P147" s="3" t="inlineStr"/>
-      <c r="Q147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R147" s="3" t="inlineStr">
-        <is>
-          <t>Страницы нет: редирект на главную.</t>
-        </is>
-      </c>
-      <c r="S147" s="3" t="inlineStr"/>
     </row>
     <row r="148" ht="58" customHeight="1">
       <c r="A148" s="3" t="n">
@@ -11612,19 +10008,6 @@
       </c>
       <c r="O148" s="3" t="inlineStr"/>
       <c r="P148" s="3" t="inlineStr"/>
-      <c r="Q148" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R148" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S148" s="3" t="inlineStr">
-        <is>
-          <t>B02f7e5</t>
-        </is>
-      </c>
     </row>
     <row r="149" ht="58" customHeight="1">
       <c r="A149" s="3" t="n">
@@ -11687,19 +10070,6 @@
       </c>
       <c r="O149" s="3" t="inlineStr"/>
       <c r="P149" s="3" t="inlineStr"/>
-      <c r="Q149" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R149" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: кнопка скачивания; ссылка скрыта до регистрации.</t>
-        </is>
-      </c>
-      <c r="S149" s="3" t="inlineStr">
-        <is>
-          <t>B3ff35a</t>
-        </is>
-      </c>
     </row>
     <row r="150" ht="58" customHeight="1">
       <c r="A150" s="3" t="n">
@@ -11762,19 +10132,6 @@
       </c>
       <c r="O150" s="3" t="inlineStr"/>
       <c r="P150" s="3" t="inlineStr"/>
-      <c r="Q150" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R150" s="3" t="inlineStr">
-        <is>
-          <t>Книга найдена в заголовке, автор совпал. Признаки размещения: скачивание epub, fb2, txt; чтение онлайн; кнопка скачивания.</t>
-        </is>
-      </c>
-      <c r="S150" s="3" t="inlineStr">
-        <is>
-          <t>B17cea6</t>
-        </is>
-      </c>
     </row>
     <row r="151" ht="58" customHeight="1">
       <c r="A151" s="3" t="n">
@@ -11837,18 +10194,9 @@
       </c>
       <c r="O151" s="3" t="inlineStr"/>
       <c r="P151" s="3" t="inlineStr"/>
-      <c r="Q151" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R151" s="3" t="inlineStr">
-        <is>
-          <t>Получен экран загрузки вместо содержимого. Нужна проверка в браузере.</t>
-        </is>
-      </c>
-      <c r="S151" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S151"/>
+  <autoFilter ref="A1:P151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15648,16 +13996,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15683,15 +14030,10 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Что не так по данным</t>
+          <t>Что не так</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Что показала страница</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Каких данных не хватает</t>
         </is>
@@ -15721,8 +14063,7 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
@@ -15752,8 +14093,7 @@
           <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
         </is>
@@ -15761,383 +14101,359 @@
     </row>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>DIGITAL ZEN</t>
+          <t>Findroid</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта.</t>
+          <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>https://skladchik.tv/threads/prompt-suno-com-ehnciklopedija-i-polnoe-rukovodstvo-po-sostavleniju-prompta-ddigital-zen.489299/</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr"/>
+          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Findroid</t>
+          <t>Ася Исай</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Гнев Империи. Книга 1</t>
+          <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
+          <t>https://kniganet.ru/romani/izmena-hochu-tvoego-muzha/</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>на какие форматы есть права: текст, аудио</t>
+          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Ася Исай</t>
+          <t>Disciplimit</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Измена. Хочу твоего мужа</t>
+          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>https://kniganet.ru/romani/izmena-hochu-tvoego-muzha/</t>
+          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Галина Колоскова, Мария Авенская</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): ИИ-проверка: Название совпадает, но указанный на странице автор Оксана Алексаева отсутствует среди кандидатов.</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="7" ht="58" customHeight="1">
       <c r="A7" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>DIGITAL ZEN</t>
+          <t>Ira Kiba</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта.</t>
+          <t>Кармические узлы в натальной карте</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>https://s4.skladchik.tv/threads/prompt-suno-com-ehnciklopedija-i-polnoe-rukovodstvo-po-sostavleniju-prompta-ddigital-zen.489299/</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+          <t>https://astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "ПРОМПТ SUNO.COM энциклопедия и полное руководство по составлению промпта." совпало, но автора из каталога (DIGITAL ZEN) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="8" ht="58" customHeight="1">
       <c r="A8" s="3" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Disciplimit</t>
+          <t>Jana Denole Яна Деноль</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Дисциплина ставок. Инструменты системного игрока. Журнал, банкролл, психология, рутина</t>
+          <t>Gaunerinnen</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>https://dolinakursov.ru/threads/disciplimit-disciplimit-sistema-kontrolja-reshenij.59305/</t>
+          <t>https://read.xbook.life/books_gaunerinnen_67131402</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
+          <t>в поле автора два написания, латиницей и кириллицей</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>основное имя автора и варианты написания</t>
         </is>
       </c>
     </row>
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Helga Duran</t>
+          <t>Armine Grigoryan</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Тарский горячий твой</t>
+          <t>Ставка на любовь</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>https://listaibuk.com/sovremennie-lyubovnie-romani/tarskiy-goryachiy-tvoy/</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Тарский горячий твой" совпало, но автора из каталога (Helga Duran) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="10" ht="58" customHeight="1">
       <c r="A10" s="3" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Ira Kiba</t>
+          <t>Lanpirot</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Кармические узлы в натальной карте</t>
+          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>https://astro-babylon.ru/biblioteca-main/karmicheskaya-astrologiya.html</t>
+          <t>https://free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2/</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>номер тома или части в адресе другой: в названии 6</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Кармическая астрология | Книги по кармической астрологии</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>серия и номер тома отдельными полями</t>
         </is>
       </c>
     </row>
     <row r="11" ht="58" customHeight="1">
       <c r="A11" s="3" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Jana Denole Яна Деноль</t>
+          <t>Larisa Lubimova</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Gaunerinnen</t>
+          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>https://read.xbook.life/books_gaunerinnen_67131402</t>
+          <t>https://librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>в поле автора два написания, латиницей и кириллицей</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>основное имя автора и варианты написания</t>
+          <t>адрес страницы не похож на название (совпало 39% слов)</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="3" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Armine Grigoryan</t>
+          <t>Елена Полярная</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Ставка на любовь</t>
+          <t>Измена. Я вас верну</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>https://mp3deer.cc/mp3/armine-grigoryan-erevani-sirun-txa</t>
+          <t>https://librain.ru/index.php/detektivy/izmena-ia-vas-vernu</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; на какие форматы есть права: текст, аудио</t>
+          <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="13" ht="58" customHeight="1">
       <c r="A13" s="3" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Lanpirot</t>
+          <t>Lilit Khachinyan</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Позывной «Хоттабыч»#6. Аватар "Х"</t>
+          <t>Guide de préparation à la production orale du DELF B2</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>https://free-kniga.ru/priklyucheniya/pozyvnoy-hottabych-7-avatar-h-ch-2/</t>
+          <t>https://languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2/</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>номер тома или части в адресе другой: в названии 6</t>
+          <t>адрес страницы не похож на название (совпало 40% слов)</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>на странице другая книга: Lanpirot. Позывной «Хоттабыч»#7. Аватар "Х" (ч.2)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>серия и номер тома отдельными полями; подтверждение правообладателя, к какой книге относится ссылка</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Lanpirot</t>
+          <t>Lost In Space</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Позывной «Хоттабыч»#9. Исчадие Кромки (ч. 2)</t>
+          <t>Наследник, которого не должно быть</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>https://readtoday.ru/priklyucheniya/pozyvnoy-hottabych-9-ischadie-kromki-ch-2/</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr"/>
+          <t>https://mp3deer.cc/mp3/%D1%81%D1%83%D0%BF%D0%B5%D1%80-%D0%B0%D1%83%D0%B4%D0%B8%D0%BE%D0%BA%D0%BD%D0%B8%D0%B3%D0%B0-%D0%BD%D0%B0%D1%81%D0%BB%D0%B5%D0%B4%D0%BD%D0%B8%D0%BA-%D0%BA%D0%BE%D1%82%D0%BE%D1%80%D0%BE%D0%B3%D0%BE-%D0%BD%D0%B5-%D0%B4%D0%BE%D0%BB%D0%B6%D0%BD%D0%BE-%D0%B1%D1%8B%D1%82%D1%8C</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>тип ebook, а ссылка похожа на аудио</t>
+        </is>
+      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+          <t>на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="3" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Larisa Lubimova</t>
+          <t>Lucy Zen</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>ОГЭ-2026 по английскому. Лайфхаки, фейлы и 100% полезной инфы Секреты письменного ОГЭ: от ошибок к совершенству Практические советы по улучшению навыков письма и грамматики.</t>
+          <t>Автономия</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>https://librain.ru/nauka-i-obrazovanie/oge-2026-po-angliiskomu-laifxaki-feily-i-100-poleznoi-infy-cast-2</t>
+          <t>https://skladmk.online/product/energiya-zhizni-lucy-zen/</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 39% слов)</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr">
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
@@ -16145,118 +14461,111 @@
     </row>
     <row r="16" ht="58" customHeight="1">
       <c r="A16" s="3" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Елена Полярная</t>
+          <t>MILA NENKA</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Измена. Я вас верну</t>
+          <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>https://librain.ru/index.php/detektivy/izmena-ia-vas-vernu</t>
+          <t>https://2ivdel.tvoysadik.ru/?section_id=98</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Арина Салай, Оксана Алексаева, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
         </is>
       </c>
     </row>
     <row r="17" ht="58" customHeight="1">
       <c r="A17" s="3" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Lilit Khachinyan</t>
+          <t>Findroid</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Guide de préparation à la production orale du DELF B2</t>
+          <t>Гнев Империи. Книга 1</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>https://languagelearning.site/french/preparation-a-lexamen-du-delf-b2-2/</t>
+          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 40% слов)</t>
+          <t>тип ebook, а ссылка похожа на аудио</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Préparation à l’examen du DELF B2 – Language Learning</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>на какие форматы есть права: текст, аудио</t>
         </is>
       </c>
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="3" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Lost In Space</t>
+          <t>Quartz Y</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Наследник, которого не должно быть</t>
+          <t>Переход в 5D измерение. Просветление. Методичка</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>https://mp3deer.cc/mp3/%D1%81%D1%83%D0%BF%D0%B5%D1%80-%D0%B0%D1%83%D0%B4%D0%B8%D0%BE%D0%BA%D0%BD%D0%B8%D0%B3%D0%B0-%D0%BD%D0%B0%D1%81%D0%BB%D0%B5%D0%B4%D0%BD%D0%B8%D0%BA-%D0%BA%D0%BE%D1%82%D0%BE%D1%80%D0%BE%D0%B3%D0%BE-%D0%BD%D0%B5-%D0%B4%D0%BE%D0%BB%D0%B6%D0%BD%D0%BE-%D0%B1%D1%8B%D1%82%D1%8C</t>
+          <t>https://librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>на какие форматы есть права: текст, аудио</t>
+          <t>адрес страницы не похож на название (совпало 25% слов)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="3" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Lucy Zen</t>
+          <t>Rais Ais Gu</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Автономия</t>
+          <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>https://skladmk.online/product/energiya-zhizni-lucy-zen/</t>
+          <t>https://skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854/</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -16264,8 +14573,7 @@
           <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
@@ -16273,52 +14581,51 @@
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="3" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Бракованный джинн</t>
+          <t>Констебль. Том III</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
+          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
         </is>
       </c>
     </row>
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="3" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>MILA NENKA</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Маленькие заботы. Мини-раскраска для самых маленьких</t>
+          <t>Медовичок</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>https://2ivdel.tvoysadik.ru/?section_id=98</t>
+          <t>https://litbox.pro/tag/ravenna/</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -16328,222 +14635,207 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Занимательные раскраски</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
         </is>
       </c>
     </row>
     <row r="22" ht="58" customHeight="1">
       <c r="A22" s="3" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Mind Wave</t>
+          <t>Галина Колоскова</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Левитация. Путь к внутренней свободе</t>
+          <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>https://mx-style.net/product/levitacziya-put-k-vnutrennej-svobode-mind-wave/</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
+          <t>https://mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Ошибка | Не удается получить доступ к сайту.</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
       <c r="A23" s="3" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Nika Nika</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Кето-рецепты</t>
+          <t>Констебль. Том III</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>https://librain.ru/zdorove/keto-recepty</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr"/>
+          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Кето-рецепты" совпало, но автора из каталога (Nika Nika) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
         </is>
       </c>
     </row>
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="3" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Nina BROD</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Тишина</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>https://aknigi24.com/book/tisina-spokoistvie-v-mire-polnom-suma-tit-nat-xan-nikosho</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr"/>
+          <t>https://free-kniga.ru/romany/tsena-proscheniya-147884/</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Тишина" совпало, но автора из каталога (Nina BROD) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="25" ht="58" customHeight="1">
       <c r="A25" s="3" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Findroid</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Гнев Империи. Книга 1</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>https://musportal.pro/track/1756600919-findroid-glava-01-gnev-imperii-kniga-1</t>
+          <t>https://gigabooks.ru/romany/tsena-proscheniya-686299/</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>тип ebook, а ссылка похожа на аудио</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>на какие форматы есть права: текст, аудио</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58" customHeight="1">
       <c r="A26" s="3" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Ominayashi</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Пять звезд. Часть 5</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>https://knigi.ebooker.online/book/42876144-kniga-pyat-zvezd.-chast-5</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
+          <t>https://librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>не нужны: размещения нет</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="3" t="n">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Quartz Y</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Переход в 5D измерение. Просветление. Методичка</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>https://librain.ru/putesestviia-i-geografiia/perexod-v-5d-tainyi-kod-dlia-zizni-bez-granic-i-boleznei</t>
+          <t>https://litseries.ru/romany/tsena-proscheniya-203253/</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 25% слов)</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Переход в 5D. Тайный код для жизни без границ и болезней.: читать и скачать онлайн бесплатно полностью fb2</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="28" ht="58" customHeight="1">
       <c r="A28" s="3" t="n">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Rais Ais Gu</t>
+          <t>Авее Лав</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Искусство простоты Навести порядок в вещах, делах и мыслях</t>
+          <t>Ценадоверия</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>https://skladchik.tv/threads/nastroit-svoj-mozg-ne-mozhesh-sosredotochitsja-zabyvaesh-vsjo-na-svete-tjanesh-s-resheniem-rais-gu.450854/</t>
+          <t>https://wav-library.net/sovremennaia-proza/cena-proshheniia</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -16553,181 +14845,167 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>на странице другая книга: Rais Ais Gu. Настроить свой мозг. Не можешь сосредоточиться? Забываешь всё на свете? Тянешь с решением?</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; подтверждение правообладателя, к какой книге относится ссылка</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="29" ht="58" customHeight="1">
       <c r="A29" s="3" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Алекс Мара</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>(Не)зачёт для птички</t>
+          <t>Разведенаипрекрасна</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>https://litbox.pro/sovremennie-lyubovnie-romani/ne-zachyot-dlya-ptichki/</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
+          <t>https://free-kniga.ru/yumor/razvedena-i-prekrasna-379393/</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "(Не)зачёт для птички" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="3" t="n">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Алекс Коган</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Бракованный джинн</t>
+          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>https://kniganet.ru/fentezi/brakovannyy-dzhinn/</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr"/>
+          <t>https://zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>адрес страницы не похож на название (совпало 29% слов)</t>
+        </is>
+      </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Бракованный джинн" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="31" ht="58" customHeight="1">
       <c r="A31" s="3" t="n">
-        <v>75</v>
+        <v>117</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Алекс Крамер</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Констебль. Том III</t>
+          <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+          <t>https://zoboko.com/book/rm9vg3d3/</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr"/>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="3" t="n">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Алекс Мара</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Медовичок</t>
+          <t>Разведенаипрекрасна</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>https://litbox.pro/tag/ravenna/</t>
+          <t>https://readtoday.ru/yumor/razvedena-i-prekrasna-727057/</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
+          <t>адрес страницы не похож на название (совпало 0% слов)</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Книги автора Равенна | LitBox | Равенна - скачать и читать все книги онлайн бесплатно полностью</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника; проверить, та ли ссылка указана для книги</t>
+          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58" customHeight="1">
       <c r="A33" s="3" t="n">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Оксана Алексаева</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Медовичок</t>
+          <t>Измена. Я вас верну</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>https://litseries.ru/romany/medovichok-533516/</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
+          <t>https://booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
+        </is>
+      </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="34" ht="58" customHeight="1">
       <c r="A34" s="3" t="n">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Галина Колоскова</t>
+          <t>Мария Авенская</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -16737,1109 +15015,142 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>https://mir-chitki.com/romany/8472-izmena-hochu-tvoego-muzha.html</t>
+          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>это же название есть у других авторов: Ася Исай, Мария Авенская</t>
+          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="35" ht="58" customHeight="1">
       <c r="A35" s="3" t="n">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Арина Салай</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Медовичок</t>
+          <t>Измена. Я вас верну</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>https://pro-books.ru/liubovnye-romany/medovicok</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
+          <t>https://wav-library.net/proza/izmena-ia-vas-vernu</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
+        </is>
+      </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58" customHeight="1">
       <c r="A36" s="3" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Мария Авенская</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Медовичок</t>
+          <t>Измена. Хочу твоего мужа</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>https://readtoday.ru/romany/medovichok-311872/</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
+          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
+        </is>
+      </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Медовичок" совпало, но автора из каталога (Ravenna) на странице нет. На странице указан автор: Юлия Ши. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58" customHeight="1">
       <c r="A37" s="3" t="n">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Полина Рей</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Констебль. Том III</t>
+          <t>Измена. Я вас верну</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>https://ruslibrary.org/fantastika-fjentezi/418-vector-sbornik-knig.html</t>
+          <t>https://pro-books.ru/proza/izmena-ia-vas-vernu</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов); похоже на страницу тега, раздела или сборника, а не одной книги</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; ссылка на страницу конкретной книги или состав сборника</t>
+          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
         </is>
       </c>
     </row>
     <row r="38" ht="58" customHeight="1">
       <c r="A38" s="3" t="n">
-        <v>87</v>
+        <v>146</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Авее Лав</t>
+          <t>Рудин Алекс</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Ценадоверия</t>
+          <t>Егерь-2: Назад в СССР</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>https://free-kniga.ru/romany/tsena-proscheniya-147884/</t>
+          <t>https://free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853/</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
+          <t>номер тома или части в адресе другой: в названии 2</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью без сокращений</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>https://gigabooks.ru/romany/tsena-proscheniya-686299/</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью бесплатно онлайн без сокращений FB2</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="58" customHeight="1">
-      <c r="A40" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>https://librain.ru/sovremennye-liubovnye-romany/cena-proshheniia</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать онлайн бесплатно полностью fb2</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="58" customHeight="1">
-      <c r="A41" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>https://litseries.ru/romany/tsena-proscheniya-203253/</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Цена прощения: читать и скачать полностью онлайн бесплатно без сокращений FB2</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="58" customHeight="1">
-      <c r="A42" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/boevik/cena-doveriia/</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Ценадоверия" совпало, но автора из каталога (Авее Лав) на странице нет. На странице указан автор: ИИ Текст. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="58" customHeight="1">
-      <c r="A43" s="3" t="n">
-        <v>96</v>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Адриана Дари</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Хозяйка Солнечного поместья</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>https://kniganet.ru/drama/nenuzhnaya-istinnaya-drakona-hozyayka-solnechnogo-pomestya/</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Хозяйка Солнечного поместья" совпало, но автора из каталога (Адриана Дари) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="58" customHeight="1">
-      <c r="A44" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Авее Лав</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Ценадоверия</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>https://wav-library.net/sovremennaia-proza/cena-proshheniia</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="58" customHeight="1">
-      <c r="A45" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Ключевской</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Тёмный маг. Книга 1. Неведомый путь</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>https://knigoline.ru/tyomnyy-mag-kniga-1-nevedomyy-put-4375/</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-    </row>
-    <row r="46" ht="58" customHeight="1">
-      <c r="A46" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Мара</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Разведенаипрекрасна</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/yumor/razvedena-i-prekrasna-379393/</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="58" customHeight="1">
-      <c r="A47" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Коган</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>https://bibliophile.top/index.php?threads/11672/</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Книга найдена в заголовке, автор совпал. Книга упомянута, но скачать, читать или слушать нельзя.</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>не нужны: размещения нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="58" customHeight="1">
-      <c r="A48" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Ключевской</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>13-й демон Асмодея. Том 2</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>https://knigoline.ru/13-y-demon-asmodeya-tom-2-9093/</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Книга найдена в заголовке, автор совпал. Есть ссылки на магазин и признаки чтения или скачивания; назначение ссылок нужно проверить.</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49" ht="58" customHeight="1">
-      <c r="A49" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Коган</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Изучаем pytest: От основ до продвинутых техник тестирования в Python</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>https://zlib.pub/book/python-testing-with-pytest-3g998v3in3tg</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 29% слов)</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Download Python Testing with pytest by Brian Okken | Python Testing with pytest EPUB</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки; проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="58" customHeight="1">
-      <c r="A50" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Крамер</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Уличная еда: рецепты блюд современного стрит-фуда</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>https://zoboko.com/book/rm9vg3d3/</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="58" customHeight="1">
-      <c r="A51" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Мара</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Пухленькая Рыженькая</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>https://libvi.ru/yumor/puhlenkaya-ryzhenkaya/</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Пухленькая Рыженькая" совпало, но автора из каталога (Алекс Мара) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="58" customHeight="1">
-      <c r="A52" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Мара</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Разведенаипрекрасна</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>https://readtoday.ru/yumor/razvedena-i-prekrasna-727057/</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>адрес страницы не похож на название (совпало 0% слов)</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>ID книги у правообладателя (артикул или ISBN) для каждой ссылки</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="58" customHeight="1">
-      <c r="A53" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Найт</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Девственность по контракту</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>https://kniganet.ru/fentezi/devstvennost-po-kontraktu/</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Девственность по контракту" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="58" customHeight="1">
-      <c r="A54" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Найт</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Жена для Синей Бороды</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>https://kniganet.ru/romani/zhena-dlya-siney-borody/</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Жена для Синей Бороды" совпало, но автора из каталога (Алекс Найт) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="58" customHeight="1">
-      <c r="A55" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Промтов</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Промтология. Большое руководство по нейросетям: от основ ИИ до готовых решений</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>https://s3.skladchinabiz.app/threads/promtologija-bolshoe-rukovodstvo-po-nejrosetjam-aleks-promtov.465616/</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="58" customHeight="1">
-      <c r="A56" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Оксана Алексаева</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>https://booksfb2.com/liubovnye-romany/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="58" customHeight="1">
-      <c r="A57" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Мария Авенская</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>Измена. Хочу твоего мужа</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="58" customHeight="1">
-      <c r="A58" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Рудин</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>Тайновидец. Том 9: Повелитель стихий</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>https://kniganet.ru/priklyucheniya/taynovidets-tom-9-povelitel-stihiy/</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: autoposter. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="58" customHeight="1">
-      <c r="A59" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Рудин</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>Тайновидец. Том 9: Повелитель стихий</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>https://libvi.ru/fentezi/taynovidets-tom-9-povelitel-stihiy/</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Тайновидец. Том 9: Повелитель стихий" совпало, но автора из каталога (Алекс Рудин) на странице нет. На странице указан автор: liv. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="58" customHeight="1">
-      <c r="A60" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Хот</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>Двойное удовольствие</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>https://knigo-lub.ru/erotika/dvoynoe-udovolstvie/</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Двойное удовольствие" совпало, но автора из каталога (Алекс Хот) на странице нет. На странице указан автор: Mery. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="58" customHeight="1">
-      <c r="A61" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Арина Салай</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>https://wav-library.net/proza/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Елена Полярная, Оксана Алексаева, Полина Рей</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="58" customHeight="1">
-      <c r="A62" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Дари Адриана</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>Хозяйка таверны "У Черных скал"</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>https://readtoday.ru/priklyucheniya/oklevetannaya-zhena-drakona-hozyayka-taverny-u-chernyh-skal-945787/</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr"/>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: ответ 404, Страница не найдена - ReadToday | 404.</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr">
-        <is>
-          <t>не нужны: страница удалена, ссылку можно закрыть</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="58" customHeight="1">
-      <c r="A63" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Мария Авенская</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>Измена. Хочу твоего мужа</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>https://knigi.fun/31487-izmena-hochu-tvoego-mugha.html</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Ася Исай, Галина Колоскова</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Измена. Хочу твоего мужа" совпало, но автора из каталога (Ася Исай, Галина Колоскова, Мария Авенская) на странице нет. На странице указан автор: Оксана Алексаева. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="58" customHeight="1">
-      <c r="A64" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Мара Алекс</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>Будь моим бывшим</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>https://litbox.pro/sovremennie-lyubovnie-romani/bud-moim-bivshim/</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 2): Название "Будь моим бывшим" совпало, но автора из каталога (Мара Алекс) на странице нет. На странице указан автор: Daniella. Нужна проверка человеком.</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>варианты имени автора и псевдонимы</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="58" customHeight="1">
-      <c r="A65" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Алекс Промтов</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Промтология. Большое руководство по нейросетям: от основ ИИ до готовых решений</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>https://skladchinabiz.app/threads/promtologija-bolshoe-rukovodstvo-po-nejrosetjam-aleks-promtov.465616/</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Курс Промтология. Большое руководство по нейросетям [Алекс Промтов] со скидкой 50%</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="58" customHeight="1">
-      <c r="A66" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Полина Рей</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>https://pro-books.ru/proza/izmena-ia-vas-vernu</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>это же название есть у других авторов: Арина Салай, Елена Полярная, Оксана Алексаева</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>на странице другая книга: Оксана Алексаева. Измена. Я вас верну</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>ID книги или ISBN, чтобы различать одноимённые книги; подтверждение правообладателя, к какой книге относится ссылка</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="58" customHeight="1">
-      <c r="A67" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Рудин Алекс</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>Егерь-2: Назад в СССР</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>https://free-kniga.ru/priklyucheniya/eger-nazad-v-sssr-669853/</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>номер тома или части в адресе другой: в названии 2</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страница прочитана, но совпадение с каталогом не найдено. Обнаружено: Егерь: назад в СССР: читать и скачать онлайн бесплатно полностью без сокращений</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>серия и номер тома отдельными полями; проверить, та ли ссылка указана для книги</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="58" customHeight="1">
-      <c r="A68" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Егорова Надежда</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Ночь на Лысой горе. Где забытые боги слышат</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>https://lllit.ru/ezoterika/noc-na-lysoi-gore-gde-zabytye-bogi-slysat</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>страница не подтвердила книгу (статус 0): Страницы нет: редирект на главную.</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>не нужны: страница удалена, ссылку можно закрыть</t>
+          <t>серия и номер тома отдельными полями</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G68"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
